--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">100013273</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>468</v>
+        <v>310</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">100013273</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F7">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013273</t>
+          <t xml:space="preserve">100013274</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,7 +390,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013273</t>
+          <t xml:space="preserve">100235936</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">122</t>
         </is>
       </c>
       <c r="F9">
-        <v>450</v>
+        <v>551</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013274</t>
+          <t xml:space="preserve">1320180</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>364</v>
+        <v>261</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">100235936</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">122</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F11">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320180</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F12">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">2519330</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>555</v>
+        <v>440</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F14">
-        <v>270</v>
+        <v>421</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2519330</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F15">
-        <v>440</v>
+        <v>1799</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">2554720</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>421</v>
+        <v>1049</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">2554720</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>1799</v>
+        <v>1314</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554720</t>
+          <t xml:space="preserve">2566043</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>1049</v>
+        <v>859</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554720</t>
+          <t xml:space="preserve">2566043</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F19">
-        <v>1314</v>
+        <v>675</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556040</t>
+          <t xml:space="preserve">2568794</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>6683</v>
+        <v>594</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563866</t>
+          <t xml:space="preserve">280121, 280122</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>6615</v>
+        <v>4049</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566043</t>
+          <t xml:space="preserve">282243, 282244</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F22">
-        <v>859</v>
+        <v>1449</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566043</t>
+          <t xml:space="preserve">283503, 283840</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>675</v>
+        <v>3100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568794</t>
+          <t xml:space="preserve">283841, 283842, 283843</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>594</v>
+        <v>5160</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">722988, 2563866</t>
+          <t xml:space="preserve">723831, 9025966</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F32">
-        <v>3629</v>
+        <v>615</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">723831, 9025966</t>
+          <t xml:space="preserve">723895, 5381817</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F33">
-        <v>615</v>
+        <v>2800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">723895, 5381817</t>
+          <t xml:space="preserve">724069, 7005749</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>2800</v>
+        <v>427</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F35">
-        <v>427</v>
+        <v>1211</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">724069, 7005749</t>
+          <t xml:space="preserve">724247, 10026465</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>1211</v>
+        <v>533</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">724247, 10026465</t>
+          <t xml:space="preserve">724248, 2519542</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>533</v>
+        <v>1788</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">724248, 2519542</t>
+          <t xml:space="preserve">724257, 2568783</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>1788</v>
+        <v>1611</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">724257, 2568783</t>
+          <t xml:space="preserve">724258, 2553804</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F39">
-        <v>1611</v>
+        <v>2415</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">724258, 2553804</t>
+          <t xml:space="preserve">724325, 1322717</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>2415</v>
+        <v>287</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">724325, 1322717</t>
+          <t xml:space="preserve">8948539</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F41">
-        <v>287</v>
+        <v>795</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948538</t>
+          <t xml:space="preserve">9018639</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948539</t>
+          <t xml:space="preserve">9802629</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F43">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018639</t>
+          <t xml:space="preserve">9874444</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">107</t>
         </is>
       </c>
       <c r="F44">
-        <v>635</v>
+        <v>2029</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,30 +2231,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025993</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
-        <v>1613</v>
+        <v>693</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200043717</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-12-30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2281,30 +2281,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9802629</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F46">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047208</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2331,30 +2331,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874444</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">107</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F47">
-        <v>2029</v>
+        <v>751</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047210</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8199232</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F48">
-        <v>501</v>
+        <v>878</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035029</t>
+          <t xml:space="preserve">200047209</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-09</t>
+          <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8199232</t>
+          <t xml:space="preserve">9025993</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F49">
-        <v>1783</v>
+        <v>1613</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035856</t>
+          <t xml:space="preserve">200055569</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-26</t>
+          <t xml:space="preserve">2021-12-06</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,35 +2481,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">9025982</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F50">
-        <v>1008</v>
+        <v>12818</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037956</t>
+          <t xml:space="preserve">311237984</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-28</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2531,35 +2531,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">2522070</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>648</v>
+        <v>11199</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037968</t>
+          <t xml:space="preserve">311247417</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-28</t>
+          <t xml:space="preserve">2027-05-15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2581,35 +2581,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">9409538</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>1233</v>
+        <v>1872</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038082</t>
+          <t xml:space="preserve">311248042</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-29</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">9844655</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,26 +2640,26 @@
         </is>
       </c>
       <c r="F53">
-        <v>693</v>
+        <v>987</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043717</t>
+          <t xml:space="preserve">311248034</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-30</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2681,35 +2681,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">5380824</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>798</v>
+        <v>11460</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047208</t>
+          <t xml:space="preserve">311248341</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-24</t>
+          <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">8297590</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F55">
-        <v>751</v>
+        <v>5478</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047210</t>
+          <t xml:space="preserve">311248979</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-24</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2781,35 +2781,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>878</v>
+        <v>2206</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047209</t>
+          <t xml:space="preserve">311252543</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-24</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025982</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F57">
-        <v>12818</v>
+        <v>4149</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237984</t>
+          <t xml:space="preserve">311252545</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2522070</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F58">
-        <v>11199</v>
+        <v>632</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247417</t>
+          <t xml:space="preserve">311252549</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-15</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9409538</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F59">
-        <v>1872</v>
+        <v>393</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248042</t>
+          <t xml:space="preserve">311252551</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9844655</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F60">
-        <v>987</v>
+        <v>1187</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248034</t>
+          <t xml:space="preserve">311252552</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380824</t>
+          <t xml:space="preserve">1323565</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,16 +3040,16 @@
         </is>
       </c>
       <c r="F61">
-        <v>11460</v>
+        <v>1708</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248341</t>
+          <t xml:space="preserve">311254120</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-18</t>
+          <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8297590</t>
+          <t xml:space="preserve">1323565</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F62">
-        <v>5478</v>
+        <v>327</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248979</t>
+          <t xml:space="preserve">311254126</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8199232</t>
+          <t xml:space="preserve">1323565</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F63">
-        <v>632</v>
+        <v>525</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250259</t>
+          <t xml:space="preserve">311254120</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">5377103</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="F64">
-        <v>2206</v>
+        <v>1255</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252543</t>
+          <t xml:space="preserve">311255423</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">5377103</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="F65">
-        <v>4149</v>
+        <v>622</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252545</t>
+          <t xml:space="preserve">311255421</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>632</v>
+        <v>1366</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252549</t>
+          <t xml:space="preserve">311255424</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F67">
-        <v>393</v>
+        <v>3189</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252551</t>
+          <t xml:space="preserve">311255427</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F68">
-        <v>1187</v>
+        <v>898</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252554</t>
+          <t xml:space="preserve">311255431</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">280121, 280122</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F69">
-        <v>4049</v>
+        <v>650</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253162</t>
+          <t xml:space="preserve">311255432</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1323565</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F70">
-        <v>1708</v>
+        <v>1381</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254120</t>
+          <t xml:space="preserve">311255434</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-15</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1323565</t>
+          <t xml:space="preserve">8901448</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>327</v>
+        <v>398</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254126</t>
+          <t xml:space="preserve">311255415</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-15</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1323565</t>
+          <t xml:space="preserve">100004809</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>525</v>
+        <v>1945</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254120</t>
+          <t xml:space="preserve">311256417</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-15</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377103</t>
+          <t xml:space="preserve">100040718</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>1255</v>
+        <v>942</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255423</t>
+          <t xml:space="preserve">311349046</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377103</t>
+          <t xml:space="preserve">2521580</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>622</v>
+        <v>304</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255421</t>
+          <t xml:space="preserve">311256415</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">7003851</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F75">
-        <v>1366</v>
+        <v>341</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255424</t>
+          <t xml:space="preserve">311256433</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">7561631</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>3189</v>
+        <v>272</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255427</t>
+          <t xml:space="preserve">311256407</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">8093023</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>898</v>
+        <v>376</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255431</t>
+          <t xml:space="preserve">311256412</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">5377127</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>650</v>
+        <v>2423</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255432</t>
+          <t xml:space="preserve">311258043</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">2523534</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>1381</v>
+        <v>456</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255434</t>
+          <t xml:space="preserve">311258394</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8901448</t>
+          <t xml:space="preserve">2525502</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255415</t>
+          <t xml:space="preserve">311258389</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100004809</t>
+          <t xml:space="preserve">2566162</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="F81">
-        <v>1945</v>
+        <v>378</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256417</t>
+          <t xml:space="preserve">311258444</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040718</t>
+          <t xml:space="preserve">2566162</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F82">
-        <v>942</v>
+        <v>390</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349046</t>
+          <t xml:space="preserve">311258445</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521580</t>
+          <t xml:space="preserve">2566162</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F83">
-        <v>304</v>
+        <v>360</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256415</t>
+          <t xml:space="preserve">311258446</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003851</t>
+          <t xml:space="preserve">5382703</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="F84">
-        <v>341</v>
+        <v>557</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256433</t>
+          <t xml:space="preserve">311258381</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7561631</t>
+          <t xml:space="preserve">7045545</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="F85">
-        <v>272</v>
+        <v>516</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256407</t>
+          <t xml:space="preserve">311258391</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8093023</t>
+          <t xml:space="preserve">9025963</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="F86">
-        <v>376</v>
+        <v>676</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256412</t>
+          <t xml:space="preserve">311258430</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377127</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>2423</v>
+        <v>2634</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258043</t>
+          <t xml:space="preserve">311259758</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2523534</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F88">
-        <v>456</v>
+        <v>266</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258394</t>
+          <t xml:space="preserve">311335367</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525502</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F89">
-        <v>428</v>
+        <v>2353</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258389</t>
+          <t xml:space="preserve">311259758</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566162</t>
+          <t xml:space="preserve">2528842</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>378</v>
+        <v>1129</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258444</t>
+          <t xml:space="preserve">311264089</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566162</t>
+          <t xml:space="preserve">2528842</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258445</t>
+          <t xml:space="preserve">311264088</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566162</t>
+          <t xml:space="preserve">2526923</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F92">
-        <v>360</v>
+        <v>281</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258446</t>
+          <t xml:space="preserve">311264737</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5382703</t>
+          <t xml:space="preserve">2526924</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4640,16 +4640,16 @@
         </is>
       </c>
       <c r="F93">
-        <v>557</v>
+        <v>638</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258381</t>
+          <t xml:space="preserve">311264743</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045545</t>
+          <t xml:space="preserve">2552585</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258391</t>
+          <t xml:space="preserve">311264772</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025963</t>
+          <t xml:space="preserve">2552585</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F95">
-        <v>676</v>
+        <v>358</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258430</t>
+          <t xml:space="preserve">311264773</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">2553620</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>2634</v>
+        <v>980</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259758</t>
+          <t xml:space="preserve">311264735</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">5378760</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>266</v>
+        <v>760</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335367</t>
+          <t xml:space="preserve">311264767</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">5379611</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>2353</v>
+        <v>987</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259758</t>
+          <t xml:space="preserve">311264761</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528842</t>
+          <t xml:space="preserve">7789017</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="F99">
-        <v>1129</v>
+        <v>661</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264089</t>
+          <t xml:space="preserve">311264749</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528842</t>
+          <t xml:space="preserve">7789017</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>440</v>
+        <v>552</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264088</t>
+          <t xml:space="preserve">311264750</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,20 +5031,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526923</t>
+          <t xml:space="preserve">8230221</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F101">
-        <v>281</v>
+        <v>1487</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264737</t>
+          <t xml:space="preserve">311264712</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526924</t>
+          <t xml:space="preserve">9864070</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5090,11 +5090,11 @@
         </is>
       </c>
       <c r="F102">
-        <v>638</v>
+        <v>1432</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264743</t>
+          <t xml:space="preserve">311264765</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552585</t>
+          <t xml:space="preserve">2519541</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="F103">
-        <v>372</v>
+        <v>1964</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264772</t>
+          <t xml:space="preserve">311264905</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-08</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552585</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>358</v>
+        <v>2198</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264773</t>
+          <t xml:space="preserve">311265419</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553620</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F105">
-        <v>980</v>
+        <v>291</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264735</t>
+          <t xml:space="preserve">311265414</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">282243, 282244</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
-        <v>1449</v>
+        <v>814</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264733</t>
+          <t xml:space="preserve">311265420</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5378760</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F107">
-        <v>760</v>
+        <v>372</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264767</t>
+          <t xml:space="preserve">311265418</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5379611</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F108">
-        <v>987</v>
+        <v>1442</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264761</t>
+          <t xml:space="preserve">311265409</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7789017</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F109">
-        <v>661</v>
+        <v>2136</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264749</t>
+          <t xml:space="preserve">311265411</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7789017</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F110">
-        <v>552</v>
+        <v>945</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264750</t>
+          <t xml:space="preserve">311265407</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8230221</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F111">
-        <v>1487</v>
+        <v>1453</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264712</t>
+          <t xml:space="preserve">311265413</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9864070</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F112">
-        <v>1432</v>
+        <v>1008</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264765</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2519541</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F113">
-        <v>1964</v>
+        <v>648</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264905</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-08</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F114">
-        <v>2198</v>
+        <v>468</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265419</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F115">
-        <v>291</v>
+        <v>640</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265414</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F116">
-        <v>814</v>
+        <v>1233</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265420</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">100019604</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F117">
-        <v>372</v>
+        <v>3714</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265418</t>
+          <t xml:space="preserve">311266053</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">100019604</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F118">
-        <v>1442</v>
+        <v>3730</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265409</t>
+          <t xml:space="preserve">311266054</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">2522967</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F119">
-        <v>2136</v>
+        <v>664</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265411</t>
+          <t xml:space="preserve">311265942</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">2553381</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>945</v>
+        <v>605</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265407</t>
+          <t xml:space="preserve">311265991</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">2568762</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F121">
-        <v>1453</v>
+        <v>398</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265413</t>
+          <t xml:space="preserve">311265989</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019604</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,11 +6090,11 @@
         </is>
       </c>
       <c r="F122">
-        <v>3714</v>
+        <v>468</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266053</t>
+          <t xml:space="preserve">311265947</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6131,20 +6131,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019604</t>
+          <t xml:space="preserve">9025966</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123">
-        <v>3730</v>
+        <v>684</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266054</t>
+          <t xml:space="preserve">311265931</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6181,20 +6181,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2522967</t>
+          <t xml:space="preserve">9025966</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F124">
-        <v>664</v>
+        <v>482</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265942</t>
+          <t xml:space="preserve">311265930</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553381</t>
+          <t xml:space="preserve">9411350</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,11 +6240,11 @@
         </is>
       </c>
       <c r="F125">
-        <v>605</v>
+        <v>930</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265991</t>
+          <t xml:space="preserve">311266000</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568762</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,11 +6290,11 @@
         </is>
       </c>
       <c r="F126">
-        <v>398</v>
+        <v>2596</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265989</t>
+          <t xml:space="preserve">311266002</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6331,20 +6331,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">9423768</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F127">
-        <v>468</v>
+        <v>558</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265947</t>
+          <t xml:space="preserve">311265934</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025966</t>
+          <t xml:space="preserve">9802629</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6390,11 +6390,11 @@
         </is>
       </c>
       <c r="F128">
-        <v>684</v>
+        <v>791</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265931</t>
+          <t xml:space="preserve">311265936</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025966</t>
+          <t xml:space="preserve">2525530</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F129">
-        <v>482</v>
+        <v>793</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265930</t>
+          <t xml:space="preserve">311266491</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411350</t>
+          <t xml:space="preserve">2525530</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F130">
-        <v>930</v>
+        <v>1601</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266000</t>
+          <t xml:space="preserve">311266492</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">2525530</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F131">
-        <v>2596</v>
+        <v>883</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266002</t>
+          <t xml:space="preserve">311266493</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9423768</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F132">
-        <v>558</v>
+        <v>288</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265934</t>
+          <t xml:space="preserve">311267481</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9802629</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="F133">
-        <v>791</v>
+        <v>468</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265936</t>
+          <t xml:space="preserve">311267489</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525530</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F134">
-        <v>793</v>
+        <v>396</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266491</t>
+          <t xml:space="preserve">311267485</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-16</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525530</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="F135">
-        <v>1601</v>
+        <v>729</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266492</t>
+          <t xml:space="preserve">311267430</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-16</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525530</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F136">
-        <v>883</v>
+        <v>468</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266493</t>
+          <t xml:space="preserve">311267418</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-16</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6836,15 +6836,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F137">
-        <v>288</v>
+        <v>468</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267481</t>
+          <t xml:space="preserve">311267421</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6886,15 +6886,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F138">
-        <v>468</v>
+        <v>396</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267489</t>
+          <t xml:space="preserve">311267410</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6931,20 +6931,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">2524028</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>396</v>
+        <v>720</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267485</t>
+          <t xml:space="preserve">311267447</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6981,20 +6981,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">5377367</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F140">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267430</t>
+          <t xml:space="preserve">311267480</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7031,20 +7031,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">8435875</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>468</v>
+        <v>330</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267418</t>
+          <t xml:space="preserve">311267435</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7081,20 +7081,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">8435875</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>468</v>
+        <v>341</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267421</t>
+          <t xml:space="preserve">311267441</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">100008684</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143">
-        <v>396</v>
+        <v>1186</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267410</t>
+          <t xml:space="preserve">311269023</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2524028</t>
+          <t xml:space="preserve">100008685</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="F144">
-        <v>720</v>
+        <v>1508</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267447</t>
+          <t xml:space="preserve">311269000</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377367</t>
+          <t xml:space="preserve">7178336</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F145">
-        <v>750</v>
+        <v>930</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267480</t>
+          <t xml:space="preserve">311269007</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8435875</t>
+          <t xml:space="preserve">9018613</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7290,16 +7290,16 @@
         </is>
       </c>
       <c r="F146">
-        <v>330</v>
+        <v>421</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267435</t>
+          <t xml:space="preserve">311269003</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8435875</t>
+          <t xml:space="preserve">2566046</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>341</v>
+        <v>252</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267441</t>
+          <t xml:space="preserve">311270527</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008684</t>
+          <t xml:space="preserve">5380892</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="F148">
-        <v>1186</v>
+        <v>416</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269023</t>
+          <t xml:space="preserve">311270530</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008685</t>
+          <t xml:space="preserve">5382761</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F149">
-        <v>1508</v>
+        <v>408</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269000</t>
+          <t xml:space="preserve">311270535</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7178336</t>
+          <t xml:space="preserve">9025977</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F150">
-        <v>930</v>
+        <v>470</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269008</t>
+          <t xml:space="preserve">311270529</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018613</t>
+          <t xml:space="preserve">9874444</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">84</t>
         </is>
       </c>
       <c r="F151">
-        <v>421</v>
+        <v>1199</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269003</t>
+          <t xml:space="preserve">311270528</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566046</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F152">
-        <v>252</v>
+        <v>468</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270527</t>
+          <t xml:space="preserve">311271986</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380892</t>
+          <t xml:space="preserve">5377582</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,16 +7640,16 @@
         </is>
       </c>
       <c r="F153">
-        <v>416</v>
+        <v>1355</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270530</t>
+          <t xml:space="preserve">311271978</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5382761</t>
+          <t xml:space="preserve">5377582</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F154">
-        <v>408</v>
+        <v>318</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270535</t>
+          <t xml:space="preserve">311271979</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025977</t>
+          <t xml:space="preserve">5378977</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7740,16 +7740,16 @@
         </is>
       </c>
       <c r="F155">
-        <v>470</v>
+        <v>650</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270529</t>
+          <t xml:space="preserve">311271982</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874444</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">84</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>1199</v>
+        <v>2799</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270528</t>
+          <t xml:space="preserve">311271972</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,20 +7831,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F157">
-        <v>468</v>
+        <v>1280</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271986</t>
+          <t xml:space="preserve">311271973</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7881,20 +7881,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377582</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F158">
-        <v>1355</v>
+        <v>1275</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271978</t>
+          <t xml:space="preserve">311271974</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7931,20 +7931,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377582</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F159">
-        <v>318</v>
+        <v>1251</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271979</t>
+          <t xml:space="preserve">311271975</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5378977</t>
+          <t xml:space="preserve">2518882</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>650</v>
+        <v>1499</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271982</t>
+          <t xml:space="preserve">311273423</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-18</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">5376904</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="F161">
-        <v>2799</v>
+        <v>704</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271972</t>
+          <t xml:space="preserve">311273416</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-18</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">2556040</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="F162">
-        <v>1280</v>
+        <v>6683</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271973</t>
+          <t xml:space="preserve">311275914</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">2556040</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F163">
-        <v>1275</v>
+        <v>762</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271974</t>
+          <t xml:space="preserve">311275914</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">2556065</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F164">
-        <v>1251</v>
+        <v>357</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271975</t>
+          <t xml:space="preserve">311275917</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518882</t>
+          <t xml:space="preserve">2521574</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>1499</v>
+        <v>640</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311273423</t>
+          <t xml:space="preserve">311276140</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-18</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376904</t>
+          <t xml:space="preserve">7055783</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="F166">
-        <v>704</v>
+        <v>921</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311273416</t>
+          <t xml:space="preserve">311276138</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-18</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556040</t>
+          <t xml:space="preserve">9993538</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F167">
-        <v>762</v>
+        <v>600</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275916</t>
+          <t xml:space="preserve">311276263</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556065</t>
+          <t xml:space="preserve">9993538</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F168">
-        <v>357</v>
+        <v>600</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275917</t>
+          <t xml:space="preserve">311276263</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,20 +8431,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521574</t>
+          <t xml:space="preserve">9993538</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F169">
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276140</t>
+          <t xml:space="preserve">311276263</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7055783</t>
+          <t xml:space="preserve">8948538</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8490,16 +8490,16 @@
         </is>
       </c>
       <c r="F170">
-        <v>921</v>
+        <v>4765</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276138</t>
+          <t xml:space="preserve">311276973</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993538</t>
+          <t xml:space="preserve">8948538</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F171">
-        <v>600</v>
+        <v>370</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276263</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993538</t>
+          <t xml:space="preserve">8948538</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F172">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276263</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993538</t>
+          <t xml:space="preserve">8948538</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F173">
-        <v>600</v>
+        <v>649</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276263</t>
+          <t xml:space="preserve">311276973</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8686,15 +8686,15 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F174">
-        <v>4765</v>
+        <v>320</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276973</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8736,15 +8736,15 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F175">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276978</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8786,15 +8786,15 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F176">
-        <v>649</v>
+        <v>1265</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276973</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8836,11 +8836,11 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F177">
-        <v>320</v>
+        <v>1380</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -8886,11 +8886,11 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F178">
-        <v>412</v>
+        <v>960</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -8936,11 +8936,11 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F179">
-        <v>1265</v>
+        <v>325</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -8986,11 +8986,11 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F180">
-        <v>1380</v>
+        <v>413</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948538</t>
+          <t xml:space="preserve">2518929</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>960</v>
+        <v>928</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311278224</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948538</t>
+          <t xml:space="preserve">2554718</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F182">
-        <v>325</v>
+        <v>623</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311278180</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948538</t>
+          <t xml:space="preserve">7045792</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F183">
-        <v>413</v>
+        <v>916</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311278170</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,20 +9181,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518929</t>
+          <t xml:space="preserve">7045792</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F184">
-        <v>928</v>
+        <v>1273</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278224</t>
+          <t xml:space="preserve">311278171</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9231,20 +9231,20 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554718</t>
+          <t xml:space="preserve">9130540</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F185">
-        <v>623</v>
+        <v>4044</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278180</t>
+          <t xml:space="preserve">311278153</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9281,20 +9281,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">283841, 283842, 283843</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F186">
-        <v>5160</v>
+        <v>2186</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278159</t>
+          <t xml:space="preserve">311278199</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045792</t>
+          <t xml:space="preserve">7515058</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -9340,16 +9340,16 @@
         </is>
       </c>
       <c r="F187">
-        <v>916</v>
+        <v>1875</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278170</t>
+          <t xml:space="preserve">311278940</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-12</t>
+          <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045792</t>
+          <t xml:space="preserve">7515058</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F188">
-        <v>1273</v>
+        <v>542</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278171</t>
+          <t xml:space="preserve">311278942</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-12</t>
+          <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130540</t>
+          <t xml:space="preserve">7515058</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F189">
-        <v>4044</v>
+        <v>493</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278153</t>
+          <t xml:space="preserve">311278941</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-12</t>
+          <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">7515058</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F190">
-        <v>2186</v>
+        <v>1186</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278199</t>
+          <t xml:space="preserve">311278942</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-12</t>
+          <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9536,15 +9536,15 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F191">
-        <v>1875</v>
+        <v>618</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278940</t>
+          <t xml:space="preserve">311278943</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9586,15 +9586,15 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F192">
-        <v>542</v>
+        <v>2576</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278942</t>
+          <t xml:space="preserve">311278944</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9636,15 +9636,15 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F193">
-        <v>493</v>
+        <v>1216</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278941</t>
+          <t xml:space="preserve">311278945</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9686,15 +9686,15 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F194">
-        <v>1186</v>
+        <v>493</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278942</t>
+          <t xml:space="preserve">311278941</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9736,15 +9736,15 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F195">
-        <v>618</v>
+        <v>493</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278943</t>
+          <t xml:space="preserve">311278941</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9786,15 +9786,15 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F196">
-        <v>2576</v>
+        <v>493</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278944</t>
+          <t xml:space="preserve">311278941</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7515058</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F197">
-        <v>1216</v>
+        <v>878</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278945</t>
+          <t xml:space="preserve">311279849</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-17</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">7515058</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F198">
-        <v>493</v>
+        <v>360</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278941</t>
+          <t xml:space="preserve">311279857</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-17</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">7515058</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F199">
-        <v>493</v>
+        <v>1151</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278941</t>
+          <t xml:space="preserve">311279850</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-17</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">7515058</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F200">
-        <v>493</v>
+        <v>1986</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278941</t>
+          <t xml:space="preserve">311279852</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-17</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10036,15 +10036,15 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F201">
-        <v>878</v>
+        <v>427</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279849</t>
+          <t xml:space="preserve">311279855</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10086,15 +10086,15 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F202">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279857</t>
+          <t xml:space="preserve">311279850</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10136,15 +10136,15 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F203">
-        <v>1151</v>
+        <v>877</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279850</t>
+          <t xml:space="preserve">311279856</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">2549637</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F204">
-        <v>1986</v>
+        <v>526</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279852</t>
+          <t xml:space="preserve">311282253</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">2554460</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F205">
-        <v>427</v>
+        <v>479</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279855</t>
+          <t xml:space="preserve">311282292</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">2554666</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F206">
-        <v>330</v>
+        <v>531</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279850</t>
+          <t xml:space="preserve">311282280</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,25 +10331,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">2555488</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F207">
-        <v>877</v>
+        <v>360</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279856</t>
+          <t xml:space="preserve">311282273</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549637</t>
+          <t xml:space="preserve">2556073</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10390,11 +10390,11 @@
         </is>
       </c>
       <c r="F208">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282253</t>
+          <t xml:space="preserve">311282264</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554460</t>
+          <t xml:space="preserve">8285703</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -10440,11 +10440,11 @@
         </is>
       </c>
       <c r="F209">
-        <v>479</v>
+        <v>1008</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282292</t>
+          <t xml:space="preserve">311282290</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554666</t>
+          <t xml:space="preserve">2526918</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="F210">
-        <v>531</v>
+        <v>3254</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282280</t>
+          <t xml:space="preserve">311283203</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-06</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2555488</t>
+          <t xml:space="preserve">2526918</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F211">
-        <v>360</v>
+        <v>448</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282273</t>
+          <t xml:space="preserve">311283201</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-06</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556073</t>
+          <t xml:space="preserve">2526918</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F212">
-        <v>530</v>
+        <v>1825</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282264</t>
+          <t xml:space="preserve">311283199</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-06</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285703</t>
+          <t xml:space="preserve">8992191</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F213">
-        <v>1008</v>
+        <v>477</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282290</t>
+          <t xml:space="preserve">311283239</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-06</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,20 +10681,20 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526918</t>
+          <t xml:space="preserve">8992191</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F214">
-        <v>3254</v>
+        <v>1632</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283203</t>
+          <t xml:space="preserve">311283241</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10731,20 +10731,20 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526918</t>
+          <t xml:space="preserve">8992191</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F215">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283201</t>
+          <t xml:space="preserve">311283240</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526918</t>
+          <t xml:space="preserve">100058876</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F216">
-        <v>1825</v>
+        <v>522</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283199</t>
+          <t xml:space="preserve">311283475</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">8992191</t>
+          <t xml:space="preserve">2555331</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F217">
-        <v>477</v>
+        <v>269</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283239</t>
+          <t xml:space="preserve">311283471</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">8992191</t>
+          <t xml:space="preserve">8154549</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F218">
-        <v>1632</v>
+        <v>14334</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283241</t>
+          <t xml:space="preserve">311283588</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8992191</t>
+          <t xml:space="preserve">8199232</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F219">
-        <v>419</v>
+        <v>501</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283240</t>
+          <t xml:space="preserve">311283491</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,20 +10981,20 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">100058876</t>
+          <t xml:space="preserve">8199232</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F220">
-        <v>522</v>
+        <v>1783</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283475</t>
+          <t xml:space="preserve">311283491</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -11031,20 +11031,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2555331</t>
+          <t xml:space="preserve">8199232</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F221">
-        <v>269</v>
+        <v>632</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283471</t>
+          <t xml:space="preserve">311283491</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -11081,20 +11081,20 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">8154549</t>
+          <t xml:space="preserve">9130926</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F222">
-        <v>14334</v>
+        <v>1900</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283588</t>
+          <t xml:space="preserve">311283476</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -11131,20 +11131,20 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130926</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F223">
-        <v>1900</v>
+        <v>3558</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283476</t>
+          <t xml:space="preserve">311283479</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -11181,20 +11181,20 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">9835382</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F224">
-        <v>3558</v>
+        <v>1025</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283479</t>
+          <t xml:space="preserve">311283466</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -11231,20 +11231,20 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835382</t>
+          <t xml:space="preserve">9948685</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F225">
-        <v>1025</v>
+        <v>616</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283466</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -11286,15 +11286,15 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F226">
-        <v>616</v>
+        <v>276</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283509</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F227">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F228">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11431,25 +11431,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9948685</t>
+          <t xml:space="preserve">2521070</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F229">
-        <v>276</v>
+        <v>3629</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311284309</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-11-17</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11481,20 +11481,20 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521070</t>
+          <t xml:space="preserve">7515058</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F230">
-        <v>3629</v>
+        <v>1078</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284309</t>
+          <t xml:space="preserve">311284307</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -11531,20 +11531,20 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">7515058</t>
+          <t xml:space="preserve">8523169</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F231">
-        <v>1078</v>
+        <v>277</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284307</t>
+          <t xml:space="preserve">311284308</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">8523169</t>
+          <t xml:space="preserve">2555839</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F232">
-        <v>277</v>
+        <v>427</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284308</t>
+          <t xml:space="preserve">311284650</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-17</t>
+          <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,20 +11631,20 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2555839</t>
+          <t xml:space="preserve">9025902</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F233">
-        <v>427</v>
+        <v>273</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284650</t>
+          <t xml:space="preserve">311284647</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025902</t>
+          <t xml:space="preserve">9124197</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -11690,11 +11690,11 @@
         </is>
       </c>
       <c r="F234">
-        <v>273</v>
+        <v>1793</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284647</t>
+          <t xml:space="preserve">311284631</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F235">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284631</t>
+          <t xml:space="preserve">311284632</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -11786,11 +11786,11 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F236">
-        <v>1793</v>
+        <v>588</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -11836,11 +11836,11 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F237">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -11881,25 +11881,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124197</t>
+          <t xml:space="preserve">5380770</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F238">
-        <v>589</v>
+        <v>4975</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284632</t>
+          <t xml:space="preserve">311285143</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-20</t>
+          <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11936,11 +11936,11 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F239">
-        <v>4975</v>
+        <v>948</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -11981,20 +11981,20 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380770</t>
+          <t xml:space="preserve">5380889</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F240">
-        <v>948</v>
+        <v>1405</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285143</t>
+          <t xml:space="preserve">311285142</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380889</t>
+          <t xml:space="preserve">5382706</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12040,11 +12040,11 @@
         </is>
       </c>
       <c r="F241">
-        <v>1405</v>
+        <v>4228</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285142</t>
+          <t xml:space="preserve">311285115</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -12081,25 +12081,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5382706</t>
+          <t xml:space="preserve">100005589</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F242">
-        <v>4228</v>
+        <v>464</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285115</t>
+          <t xml:space="preserve">311285853</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-22</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,20 +12131,20 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005589</t>
+          <t xml:space="preserve">2565303</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F243">
-        <v>464</v>
+        <v>2045</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285853</t>
+          <t xml:space="preserve">311285802</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -12186,15 +12186,15 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F244">
-        <v>2045</v>
+        <v>371</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285802</t>
+          <t xml:space="preserve">311285803</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F245">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285803</t>
+          <t xml:space="preserve">311285801</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -12281,25 +12281,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2565303</t>
+          <t xml:space="preserve">8192189</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F246">
-        <v>371</v>
+        <v>445</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285801</t>
+          <t xml:space="preserve">311286034</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">8192189</t>
+          <t xml:space="preserve">5377816</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -12340,16 +12340,16 @@
         </is>
       </c>
       <c r="F247">
-        <v>445</v>
+        <v>1926</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286034</t>
+          <t xml:space="preserve">311286334</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377816</t>
+          <t xml:space="preserve">5377830</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -12390,11 +12390,11 @@
         </is>
       </c>
       <c r="F248">
-        <v>1926</v>
+        <v>554</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286334</t>
+          <t xml:space="preserve">311286332</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -12436,15 +12436,15 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F249">
-        <v>554</v>
+        <v>284</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286332</t>
+          <t xml:space="preserve">311286331</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F250">
@@ -12531,25 +12531,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377830</t>
+          <t xml:space="preserve">2518884</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F251">
-        <v>284</v>
+        <v>820</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286331</t>
+          <t xml:space="preserve">311286568</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518884</t>
+          <t xml:space="preserve">2528563</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -12590,11 +12590,11 @@
         </is>
       </c>
       <c r="F252">
-        <v>820</v>
+        <v>1340</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286568</t>
+          <t xml:space="preserve">311286570</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528563</t>
+          <t xml:space="preserve">7003883</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -12640,16 +12640,16 @@
         </is>
       </c>
       <c r="F253">
-        <v>1340</v>
+        <v>2462</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286570</t>
+          <t xml:space="preserve">311286773</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-01</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12686,15 +12686,15 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F254">
-        <v>2462</v>
+        <v>1909</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286774</t>
+          <t xml:space="preserve">311286773</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -12731,20 +12731,20 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003883</t>
+          <t xml:space="preserve">8230221</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F255">
-        <v>1909</v>
+        <v>9563</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286774</t>
+          <t xml:space="preserve">311286776</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -12786,15 +12786,15 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F256">
-        <v>9563</v>
+        <v>940</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286776</t>
+          <t xml:space="preserve">311286775</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -12831,25 +12831,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">8230221</t>
+          <t xml:space="preserve">7196771</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F257">
-        <v>940</v>
+        <v>406</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286775</t>
+          <t xml:space="preserve">311286986</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-01</t>
+          <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12886,15 +12886,15 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F258">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286986</t>
+          <t xml:space="preserve">311286963</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F259">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286963</t>
+          <t xml:space="preserve">311286987</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -12986,15 +12986,15 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F260">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286987</t>
+          <t xml:space="preserve">311286988</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F261">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286988</t>
+          <t xml:space="preserve">311286989</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F262">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286989</t>
+          <t xml:space="preserve">311286990</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -13136,15 +13136,15 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F263">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286990</t>
+          <t xml:space="preserve">311286960</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F264">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286960</t>
+          <t xml:space="preserve">311286961</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F265">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286961</t>
+          <t xml:space="preserve">311286962</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -13281,20 +13281,20 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196771</t>
+          <t xml:space="preserve">8115385</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F266">
-        <v>407</v>
+        <v>983</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286962</t>
+          <t xml:space="preserve">311286976</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -13336,15 +13336,15 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F267">
-        <v>983</v>
+        <v>460</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286976</t>
+          <t xml:space="preserve">311286977</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -13386,15 +13386,15 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F268">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286977</t>
+          <t xml:space="preserve">311286978</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -13431,20 +13431,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">8115385</t>
+          <t xml:space="preserve">9130468</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F269">
-        <v>490</v>
+        <v>4476</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286978</t>
+          <t xml:space="preserve">311287008</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -13486,15 +13486,15 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F270">
-        <v>4476</v>
+        <v>1320</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287008</t>
+          <t xml:space="preserve">311287009</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -13531,25 +13531,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130468</t>
+          <t xml:space="preserve">7196771</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F271">
-        <v>1320</v>
+        <v>406</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287009</t>
+          <t xml:space="preserve">311287830</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-04</t>
+          <t xml:space="preserve">2027-12-08</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -13581,20 +13581,20 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196771</t>
+          <t xml:space="preserve">9993537</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F272">
-        <v>406</v>
+        <v>608</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287830</t>
+          <t xml:space="preserve">311287819</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993537</t>
+          <t xml:space="preserve">9018641</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -13640,16 +13640,16 @@
         </is>
       </c>
       <c r="F273">
-        <v>608</v>
+        <v>1156</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287819</t>
+          <t xml:space="preserve">311288520</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-08</t>
+          <t xml:space="preserve">2027-12-13</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -13686,11 +13686,11 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F274">
-        <v>1156</v>
+        <v>368</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -13731,25 +13731,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018641</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F275">
-        <v>368</v>
+        <v>1263</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288520</t>
+          <t xml:space="preserve">311288809</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-13</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -13781,20 +13781,20 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">8746444</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F276">
-        <v>1263</v>
+        <v>1046</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288809</t>
+          <t xml:space="preserve">311288798</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -13831,20 +13831,20 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">8746444</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F277">
-        <v>1046</v>
+        <v>931</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288798</t>
+          <t xml:space="preserve">311288796</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -13886,15 +13886,15 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F278">
-        <v>931</v>
+        <v>946</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288796</t>
+          <t xml:space="preserve">311288794</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -13936,15 +13936,15 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F279">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288794</t>
+          <t xml:space="preserve">311288792</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -13981,25 +13981,25 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F280">
-        <v>932</v>
+        <v>589</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288792</t>
+          <t xml:space="preserve">311288912</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -14031,20 +14031,20 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">8746444</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F281">
-        <v>589</v>
+        <v>1058</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288912</t>
+          <t xml:space="preserve">311288987</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -14086,15 +14086,15 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F282">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288987</t>
+          <t xml:space="preserve">311288990</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -14131,25 +14131,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">8746444</t>
+          <t xml:space="preserve">100004810</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F283">
-        <v>1046</v>
+        <v>480</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288990</t>
+          <t xml:space="preserve">311289149</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -14186,15 +14186,15 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F284">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289149</t>
+          <t xml:space="preserve">311289150</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F285">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289150</t>
+          <t xml:space="preserve">311289151</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -14286,15 +14286,15 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F286">
-        <v>504</v>
+        <v>252</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289151</t>
+          <t xml:space="preserve">311289152</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -14331,20 +14331,20 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">100004810</t>
+          <t xml:space="preserve">2564018</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F287">
-        <v>252</v>
+        <v>396</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289152</t>
+          <t xml:space="preserve">311289158</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -14381,20 +14381,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564018</t>
+          <t xml:space="preserve">2566043</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F288">
-        <v>396</v>
+        <v>593</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289158</t>
+          <t xml:space="preserve">311289142</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -14431,20 +14431,20 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566043</t>
+          <t xml:space="preserve">5376934</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F289">
-        <v>593</v>
+        <v>397</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289142</t>
+          <t xml:space="preserve">311289153</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">283503, 283840</t>
+          <t xml:space="preserve">5380077</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -14490,11 +14490,11 @@
         </is>
       </c>
       <c r="F290">
-        <v>3100</v>
+        <v>334</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289255</t>
+          <t xml:space="preserve">311289160</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -14531,20 +14531,20 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376934</t>
+          <t xml:space="preserve">5381277</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F291">
-        <v>397</v>
+        <v>285</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289153</t>
+          <t xml:space="preserve">311289156</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -14581,20 +14581,20 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380077</t>
+          <t xml:space="preserve">5381277</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F292">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289160</t>
+          <t xml:space="preserve">311289156</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F293">
@@ -14681,20 +14681,20 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381277</t>
+          <t xml:space="preserve">7045143</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F294">
-        <v>285</v>
+        <v>480</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289156</t>
+          <t xml:space="preserve">311289148</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -14731,20 +14731,20 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381277</t>
+          <t xml:space="preserve">7196772</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F295">
-        <v>285</v>
+        <v>417</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289156</t>
+          <t xml:space="preserve">311289144</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -14781,20 +14781,20 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045143</t>
+          <t xml:space="preserve">7196772</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F296">
-        <v>480</v>
+        <v>417</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289148</t>
+          <t xml:space="preserve">311289144</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196772</t>
+          <t xml:space="preserve">7751582</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -14840,11 +14840,11 @@
         </is>
       </c>
       <c r="F297">
-        <v>417</v>
+        <v>2147</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289144</t>
+          <t xml:space="preserve">311289139</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196772</t>
+          <t xml:space="preserve">7751582</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -14890,11 +14890,11 @@
         </is>
       </c>
       <c r="F298">
-        <v>417</v>
+        <v>309</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289144</t>
+          <t xml:space="preserve">311289140</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">7751582</t>
+          <t xml:space="preserve">2521536</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -14940,16 +14940,16 @@
         </is>
       </c>
       <c r="F299">
-        <v>2147</v>
+        <v>861</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289139</t>
+          <t xml:space="preserve">311290137</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -14981,25 +14981,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">7751582</t>
+          <t xml:space="preserve">5378771</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F300">
-        <v>309</v>
+        <v>1230</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289140</t>
+          <t xml:space="preserve">311290511</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521536</t>
+          <t xml:space="preserve">9027658</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -15040,16 +15040,16 @@
         </is>
       </c>
       <c r="F301">
-        <v>861</v>
+        <v>1172</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290137</t>
+          <t xml:space="preserve">311290522</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5378771</t>
+          <t xml:space="preserve">5378206</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -15090,16 +15090,16 @@
         </is>
       </c>
       <c r="F302">
-        <v>1230</v>
+        <v>3075</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290511</t>
+          <t xml:space="preserve">311290714</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">9027658</t>
+          <t xml:space="preserve">7045127</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -15140,16 +15140,16 @@
         </is>
       </c>
       <c r="F303">
-        <v>1172</v>
+        <v>4108</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290522</t>
+          <t xml:space="preserve">311290712</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -15181,20 +15181,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5378206</t>
+          <t xml:space="preserve">7045127</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F304">
-        <v>3075</v>
+        <v>854</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290714</t>
+          <t xml:space="preserve">311290713</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045127</t>
+          <t xml:space="preserve">100019604</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -15240,16 +15240,16 @@
         </is>
       </c>
       <c r="F305">
-        <v>4108</v>
+        <v>1923</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290712</t>
+          <t xml:space="preserve">311290748</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -15281,25 +15281,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045127</t>
+          <t xml:space="preserve">5382915</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F306">
-        <v>854</v>
+        <v>607</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290713</t>
+          <t xml:space="preserve">311290746</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -15331,20 +15331,20 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019604</t>
+          <t xml:space="preserve">5382915</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F307">
-        <v>1923</v>
+        <v>512</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290748</t>
+          <t xml:space="preserve">311290747</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -15381,20 +15381,20 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">5382915</t>
+          <t xml:space="preserve">9025993</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F308">
-        <v>607</v>
+        <v>2650</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290746</t>
+          <t xml:space="preserve">311290749</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -15431,25 +15431,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">5382915</t>
+          <t xml:space="preserve">8992191</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F309">
-        <v>512</v>
+        <v>2988</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290747</t>
+          <t xml:space="preserve">311290837</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -15481,25 +15481,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025993</t>
+          <t xml:space="preserve">8992191</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F310">
-        <v>2650</v>
+        <v>1937</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290749</t>
+          <t xml:space="preserve">311290837</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -15536,11 +15536,11 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F311">
-        <v>2988</v>
+        <v>720</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -15586,11 +15586,11 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F312">
-        <v>1937</v>
+        <v>946</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -15636,11 +15636,11 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F313">
-        <v>720</v>
+        <v>1370</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -15686,11 +15686,11 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F314">
-        <v>946</v>
+        <v>881</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -15731,25 +15731,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">8992191</t>
+          <t xml:space="preserve">9746781</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F315">
-        <v>1370</v>
+        <v>1628</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290837</t>
+          <t xml:space="preserve">311290921</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-02</t>
+          <t xml:space="preserve">2028-01-03</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -15781,25 +15781,25 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">8992191</t>
+          <t xml:space="preserve">9018641</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F316">
-        <v>881</v>
+        <v>777</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290837</t>
+          <t xml:space="preserve">311291684</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-02</t>
+          <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -15831,25 +15831,25 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">9746781</t>
+          <t xml:space="preserve">9018641</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F317">
-        <v>1628</v>
+        <v>820</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290921</t>
+          <t xml:space="preserve">311291684</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-03</t>
+          <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -15886,11 +15886,11 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F318">
-        <v>777</v>
+        <v>645</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -15931,20 +15931,20 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018641</t>
+          <t xml:space="preserve">9025993</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F319">
-        <v>820</v>
+        <v>375</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291684</t>
+          <t xml:space="preserve">311291806</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -15981,20 +15981,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018641</t>
+          <t xml:space="preserve">9874447</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F320">
-        <v>645</v>
+        <v>1738</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291684</t>
+          <t xml:space="preserve">311291678</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025993</t>
+          <t xml:space="preserve">9133953</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -16040,16 +16040,16 @@
         </is>
       </c>
       <c r="F321">
-        <v>375</v>
+        <v>2130</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291806</t>
+          <t xml:space="preserve">311296823</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-09</t>
+          <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -16081,25 +16081,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874447</t>
+          <t xml:space="preserve">9133953</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F322">
-        <v>1738</v>
+        <v>2130</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291678</t>
+          <t xml:space="preserve">311296824</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-09</t>
+          <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -16131,25 +16131,25 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">9133953</t>
+          <t xml:space="preserve">7515058</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F323">
-        <v>2130</v>
+        <v>1895</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296823</t>
+          <t xml:space="preserve">311468256</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-08</t>
+          <t xml:space="preserve">2030-10-20</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -16181,25 +16181,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">9133953</t>
+          <t xml:space="preserve">8298401</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F324">
-        <v>2130</v>
+        <v>3929</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296824</t>
+          <t xml:space="preserve">311588799</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-08</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -16231,25 +16231,25 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">7515058</t>
+          <t xml:space="preserve">2563866</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F325">
-        <v>1895</v>
+        <v>6615</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468256</t>
+          <t xml:space="preserve">311734407</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-20</t>
+          <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -16281,25 +16281,25 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">8298401</t>
+          <t xml:space="preserve">722988, 2563866</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F326">
-        <v>3929</v>
+        <v>3629</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588799</t>
+          <t xml:space="preserve">311734407</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">

--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 15</t>
+          <t xml:space="preserve">Axeltorv 6P</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005589</t>
+          <t xml:space="preserve">5377485</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H2">
-        <v>580</v>
+        <v>1837</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 8</t>
+          <t xml:space="preserve">Brolæggervænget 14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005589</t>
+          <t xml:space="preserve">724247, 10026465</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>665</v>
+        <v>533</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 6</t>
+          <t xml:space="preserve">Brøderupvej 2A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005589</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H4">
-        <v>804</v>
+        <v>1799</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 4</t>
+          <t xml:space="preserve">Byagervej 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005589</t>
+          <t xml:space="preserve">722977, 2518927</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H5">
-        <v>818</v>
+        <v>2218</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 17</t>
+          <t xml:space="preserve">Byagervej 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013273</t>
+          <t xml:space="preserve">722977, 2518927</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H6">
-        <v>310</v>
+        <v>703</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 19</t>
+          <t xml:space="preserve">Byagervej 2A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013273</t>
+          <t xml:space="preserve">722980, 2518927</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H7">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 9</t>
+          <t xml:space="preserve">Engvej 22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013274</t>
+          <t xml:space="preserve">5383231</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>364</v>
+        <v>975</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glasværksvej 72</t>
+          <t xml:space="preserve">Glasværksvej 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">100235936</t>
+          <t xml:space="preserve">724258, 2553804</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">122</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H9">
-        <v>551</v>
+        <v>2415</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovalle 17</t>
+          <t xml:space="preserve">Glasværksvej 72</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320180</t>
+          <t xml:space="preserve">100235936</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">122</t>
         </is>
       </c>
       <c r="H10">
-        <v>261</v>
+        <v>551</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvedvej 22</t>
+          <t xml:space="preserve">Gormsvej 5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">9802629</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>555</v>
+        <v>791</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvedvej 20</t>
+          <t xml:space="preserve">Grønbrovej 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4262</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">724248, 2519542</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>270</v>
+        <v>1788</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstvedvej 10</t>
+          <t xml:space="preserve">Grønnegade 10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2519330</t>
+          <t xml:space="preserve">5376988</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H13">
-        <v>440</v>
+        <v>946</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,17 +811,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korskildevej 2B</t>
+          <t xml:space="preserve">Grønnegade 10H</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">5376988</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="H14">
-        <v>421</v>
+        <v>486</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøderupvej 2A</t>
+          <t xml:space="preserve">Kasernevej 15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">9874444</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">107</t>
         </is>
       </c>
       <c r="H15">
-        <v>1799</v>
+        <v>2029</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvænget 19</t>
+          <t xml:space="preserve">Kildegårdsvej 56</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554720</t>
+          <t xml:space="preserve">8948539</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H16">
-        <v>1049</v>
+        <v>795</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvænget 12</t>
+          <t xml:space="preserve">Kohavevej 10A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554720</t>
+          <t xml:space="preserve">724069, 7005749</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>1314</v>
+        <v>427</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebæksholm 1</t>
+          <t xml:space="preserve">Kohavevej 10B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566043</t>
+          <t xml:space="preserve">724069, 7005749</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H18">
-        <v>859</v>
+        <v>1211</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebæksholm 1A</t>
+          <t xml:space="preserve">Korskildevej 2B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566043</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H19">
-        <v>675</v>
+        <v>421</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,17 +1171,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toksværd Bygade 2</t>
+          <t xml:space="preserve">Mogenstrup Parkvej 8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568794</t>
+          <t xml:space="preserve">9018639</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="H20">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 54</t>
+          <t xml:space="preserve">Nygårdsvej 102B</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">280121, 280122</t>
+          <t xml:space="preserve">723895, 5381817</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H21">
-        <v>4049</v>
+        <v>2800</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 1</t>
+          <t xml:space="preserve">Næstvedvej 10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">282243, 282244</t>
+          <t xml:space="preserve">2519330</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H22">
-        <v>1449</v>
+        <v>440</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 2B</t>
+          <t xml:space="preserve">Rolighedsvej 25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">283503, 283840</t>
+          <t xml:space="preserve">723831, 9025966</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H23">
-        <v>3100</v>
+        <v>615</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkebjerg Alle 7</t>
+          <t xml:space="preserve">Rønnebæksholm 1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">283841, 283842, 283843</t>
+          <t xml:space="preserve">2566043</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="H24">
-        <v>5160</v>
+        <v>859</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 10H</t>
+          <t xml:space="preserve">Rønnebæksholm 1A</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376988</t>
+          <t xml:space="preserve">2566043</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H25">
-        <v>486</v>
+        <v>675</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,26 +1531,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 10</t>
+          <t xml:space="preserve">Sandvedvej 20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376988</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H26">
-        <v>946</v>
+        <v>270</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,26 +1591,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axeltorv 6P</t>
+          <t xml:space="preserve">Sandvedvej 22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377485</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H27">
-        <v>1837</v>
+        <v>555</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 22</t>
+          <t xml:space="preserve">Skovalle 17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383231</t>
+          <t xml:space="preserve">1320180</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="H28">
-        <v>975</v>
+        <v>261</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,26 +1711,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 2</t>
+          <t xml:space="preserve">Sletskovvej 5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">722977, 2518927</t>
+          <t xml:space="preserve">724325, 1322717</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H29">
-        <v>2218</v>
+        <v>287</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 2</t>
+          <t xml:space="preserve">Søvænget 12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4171</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">722977, 2518927</t>
+          <t xml:space="preserve">2554720</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H30">
-        <v>703</v>
+        <v>1314</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 2A</t>
+          <t xml:space="preserve">Søvænget 19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4171</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">722980, 2518927</t>
+          <t xml:space="preserve">2554720</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>419</v>
+        <v>1049</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 25</t>
+          <t xml:space="preserve">Tokesvej 2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">723831, 9025966</t>
+          <t xml:space="preserve">724257, 2568783</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>615</v>
+        <v>1611</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 102B</t>
+          <t xml:space="preserve">Toksværd Bygade 2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">723895, 5381817</t>
+          <t xml:space="preserve">2568794</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>2800</v>
+        <v>594</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kohavevej 10A</t>
+          <t xml:space="preserve">Tommerupvej 9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">724069, 7005749</t>
+          <t xml:space="preserve">100013274</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="H34">
-        <v>427</v>
+        <v>364</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kohavevej 10B</t>
+          <t xml:space="preserve">Troensevej 15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">724069, 7005749</t>
+          <t xml:space="preserve">100005589</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="H35">
-        <v>1211</v>
+        <v>580</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervænget 14</t>
+          <t xml:space="preserve">Troensevej 17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">724247, 10026465</t>
+          <t xml:space="preserve">100013273</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="H36">
-        <v>533</v>
+        <v>310</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønbrovej 1</t>
+          <t xml:space="preserve">Troensevej 19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4262</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">724248, 2519542</t>
+          <t xml:space="preserve">100013273</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="H37">
-        <v>1788</v>
+        <v>450</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tokesvej 2</t>
+          <t xml:space="preserve">Troensevej 4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">724257, 2568783</t>
+          <t xml:space="preserve">100005589</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="H38">
-        <v>1611</v>
+        <v>818</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glasværksvej 1</t>
+          <t xml:space="preserve">Troensevej 6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">724258, 2553804</t>
+          <t xml:space="preserve">100005589</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="H39">
-        <v>2415</v>
+        <v>804</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sletskovvej 5</t>
+          <t xml:space="preserve">Troensevej 8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">724325, 1322717</t>
+          <t xml:space="preserve">100005589</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="H40">
-        <v>287</v>
+        <v>665</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,40 +2431,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdsvej 56</t>
+          <t xml:space="preserve">Nygårdsvej 62</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948539</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>795</v>
+        <v>693</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200043717</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-12-30</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mogenstrup Parkvej 8</t>
+          <t xml:space="preserve">Parkvej 142</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,30 +2501,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018639</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H42">
-        <v>635</v>
+        <v>798</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047208</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2551,40 +2551,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 5</t>
+          <t xml:space="preserve">Parkvej 144</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9802629</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H43">
-        <v>791</v>
+        <v>751</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047210</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 15</t>
+          <t xml:space="preserve">Parkvej 146</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874444</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">107</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H44">
-        <v>2029</v>
+        <v>878</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047209</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 62</t>
+          <t xml:space="preserve">Grimstrupvej 131A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">9025993</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H45">
-        <v>693</v>
+        <v>1613</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043717</t>
+          <t xml:space="preserve">200055569</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-30</t>
+          <t xml:space="preserve">2021-12-06</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 142</t>
+          <t xml:space="preserve">Parkvej 109A</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,35 +2741,35 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">9025982</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>798</v>
+        <v>12818</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047208</t>
+          <t xml:space="preserve">311237984</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-24</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 144</t>
+          <t xml:space="preserve">Solsikkevej 20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,35 +2801,35 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">2522070</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
-        <v>751</v>
+        <v>11199</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047210</t>
+          <t xml:space="preserve">311247417</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-24</t>
+          <t xml:space="preserve">2027-05-15</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 146</t>
+          <t xml:space="preserve">Eskadronsvej 1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,35 +2861,35 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">9409538</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>878</v>
+        <v>1872</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047209</t>
+          <t xml:space="preserve">311248042</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-24</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimstrupvej 131A</t>
+          <t xml:space="preserve">Mælkevejen 1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,35 +2921,35 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025993</t>
+          <t xml:space="preserve">9844655</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>1613</v>
+        <v>987</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055569</t>
+          <t xml:space="preserve">311248034</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-06</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 109A</t>
+          <t xml:space="preserve">Manøvej 22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025982</t>
+          <t xml:space="preserve">5380824</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="H50">
-        <v>12818</v>
+        <v>11460</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237984</t>
+          <t xml:space="preserve">311248341</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 20</t>
+          <t xml:space="preserve">Birkebjerg Alle 1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,25 +3041,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2522070</t>
+          <t xml:space="preserve">8297590</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="H51">
-        <v>11199</v>
+        <v>5478</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247417</t>
+          <t xml:space="preserve">311248979</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-15</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskadronsvej 1</t>
+          <t xml:space="preserve">Kildemarksvej 67</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9409538</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="H52">
-        <v>1872</v>
+        <v>2206</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248042</t>
+          <t xml:space="preserve">311252543</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mælkevejen 1</t>
+          <t xml:space="preserve">Kildemarksvej 67</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,25 +3161,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9844655</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H53">
-        <v>987</v>
+        <v>4149</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248034</t>
+          <t xml:space="preserve">311252545</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manøvej 22</t>
+          <t xml:space="preserve">Kildemarksvej 67</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,25 +3221,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380824</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H54">
-        <v>11460</v>
+        <v>393</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248341</t>
+          <t xml:space="preserve">311252551</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-18</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkebjerg Alle 1</t>
+          <t xml:space="preserve">Kærmindevej 2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8297590</t>
+          <t xml:space="preserve">9025955</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H55">
-        <v>5478</v>
+        <v>632</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248979</t>
+          <t xml:space="preserve">311252549</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 67</t>
+          <t xml:space="preserve">Kærmindevej 2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,15 +3346,15 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H56">
-        <v>2206</v>
+        <v>1187</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252543</t>
+          <t xml:space="preserve">311252554</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 67</t>
+          <t xml:space="preserve">Farimagsvej 54</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,25 +3401,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">280121, 280122</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H57">
-        <v>4149</v>
+        <v>4049</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252545</t>
+          <t xml:space="preserve">311253162</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærmindevej 2</t>
+          <t xml:space="preserve">Englebjergvej 12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">1323565</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>632</v>
+        <v>1708</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252549</t>
+          <t xml:space="preserve">311254120</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 67</t>
+          <t xml:space="preserve">Englebjergvej 12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,25 +3521,25 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">1323565</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H59">
-        <v>393</v>
+        <v>525</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252551</t>
+          <t xml:space="preserve">311254120</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærmindevej 2</t>
+          <t xml:space="preserve">Englebjergvej 14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025955</t>
+          <t xml:space="preserve">1323565</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H60">
-        <v>1187</v>
+        <v>327</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252554</t>
+          <t xml:space="preserve">311254126</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-08</t>
+          <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Englebjergvej 12</t>
+          <t xml:space="preserve">Jernbanegade 10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1323565</t>
+          <t xml:space="preserve">5377103</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3650,16 +3650,16 @@
         </is>
       </c>
       <c r="H61">
-        <v>1708</v>
+        <v>1255</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254120</t>
+          <t xml:space="preserve">311255423</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-15</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Englebjergvej 14</t>
+          <t xml:space="preserve">Jernbanegade 10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1323565</t>
+          <t xml:space="preserve">5377103</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="H62">
-        <v>327</v>
+        <v>622</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254126</t>
+          <t xml:space="preserve">311255421</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-15</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Englebjergvej 12</t>
+          <t xml:space="preserve">Lille Englebjergvej 3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,25 +3761,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1323565</t>
+          <t xml:space="preserve">8901448</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>525</v>
+        <v>398</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254120</t>
+          <t xml:space="preserve">311255415</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-15</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 10</t>
+          <t xml:space="preserve">Nygårdsvej 62</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,20 +3821,20 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377103</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>1255</v>
+        <v>1366</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255423</t>
+          <t xml:space="preserve">311255424</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 10</t>
+          <t xml:space="preserve">Nygårdsvej 62</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,20 +3881,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377103</t>
+          <t xml:space="preserve">5380901</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H65">
-        <v>622</v>
+        <v>3189</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255421</t>
+          <t xml:space="preserve">311255427</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3946,15 +3946,15 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H66">
-        <v>1366</v>
+        <v>898</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255424</t>
+          <t xml:space="preserve">311255431</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4006,15 +4006,15 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H67">
-        <v>3189</v>
+        <v>650</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255427</t>
+          <t xml:space="preserve">311255432</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4066,15 +4066,15 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H68">
-        <v>898</v>
+        <v>1381</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255431</t>
+          <t xml:space="preserve">311255434</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 62</t>
+          <t xml:space="preserve">Bygårdsvej 9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">7561631</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H69">
-        <v>650</v>
+        <v>272</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255432</t>
+          <t xml:space="preserve">311256407</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 62</t>
+          <t xml:space="preserve">Farimagsvej 52</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380901</t>
+          <t xml:space="preserve">100004809</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>1381</v>
+        <v>1945</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255434</t>
+          <t xml:space="preserve">311256417</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Englebjergvej 3</t>
+          <t xml:space="preserve">Hasselvej 14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8901448</t>
+          <t xml:space="preserve">7003851</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>398</v>
+        <v>341</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255415</t>
+          <t xml:space="preserve">311256433</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 52</t>
+          <t xml:space="preserve">Hindholmvej 15</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100004809</t>
+          <t xml:space="preserve">8093023</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,11 +4310,11 @@
         </is>
       </c>
       <c r="H72">
-        <v>1945</v>
+        <v>376</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256417</t>
+          <t xml:space="preserve">311256412</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orionvej 60</t>
+          <t xml:space="preserve">Lillevang 2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040718</t>
+          <t xml:space="preserve">2521580</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,11 +4370,11 @@
         </is>
       </c>
       <c r="H73">
-        <v>942</v>
+        <v>304</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349046</t>
+          <t xml:space="preserve">311256415</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lillevang 2</t>
+          <t xml:space="preserve">Orionvej 60</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521580</t>
+          <t xml:space="preserve">100040718</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,11 +4430,11 @@
         </is>
       </c>
       <c r="H74">
-        <v>304</v>
+        <v>942</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256415</t>
+          <t xml:space="preserve">311349046</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hasselvej 14</t>
+          <t xml:space="preserve">Jernbanegade 12N</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003851</t>
+          <t xml:space="preserve">5377127</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>341</v>
+        <v>2423</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256433</t>
+          <t xml:space="preserve">311258043</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygårdsvej 9</t>
+          <t xml:space="preserve">Birkehegnet 96</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7561631</t>
+          <t xml:space="preserve">5382703</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>272</v>
+        <v>557</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256407</t>
+          <t xml:space="preserve">311258381</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindholmvej 15</t>
+          <t xml:space="preserve">Dyssegårdsvej 2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8093023</t>
+          <t xml:space="preserve">2566162</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,16 +4610,16 @@
         </is>
       </c>
       <c r="H77">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256412</t>
+          <t xml:space="preserve">311258444</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 12N</t>
+          <t xml:space="preserve">Dyssegårdsvej 4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,25 +4661,25 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377127</t>
+          <t xml:space="preserve">2566162</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H78">
-        <v>2423</v>
+        <v>390</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258047</t>
+          <t xml:space="preserve">311258445</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fodbygårdsvej 137</t>
+          <t xml:space="preserve">Dyssegårdsvej 6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,20 +4721,20 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2523534</t>
+          <t xml:space="preserve">2566162</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H79">
-        <v>456</v>
+        <v>360</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258394</t>
+          <t xml:space="preserve">311258446</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jenstrupvej 19</t>
+          <t xml:space="preserve">Ejlersvej 22</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525502</t>
+          <t xml:space="preserve">9025963</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,11 +4790,11 @@
         </is>
       </c>
       <c r="H80">
-        <v>428</v>
+        <v>676</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258389</t>
+          <t xml:space="preserve">311258430</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyssegårdsvej 2</t>
+          <t xml:space="preserve">Fodbygårdsvej 137</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566162</t>
+          <t xml:space="preserve">2523534</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,11 +4850,11 @@
         </is>
       </c>
       <c r="H81">
-        <v>378</v>
+        <v>456</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258444</t>
+          <t xml:space="preserve">311258394</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyssegårdsvej 4</t>
+          <t xml:space="preserve">Jenstrupvej 19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,20 +4901,20 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566162</t>
+          <t xml:space="preserve">2525502</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258445</t>
+          <t xml:space="preserve">311258389</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyssegårdsvej 6</t>
+          <t xml:space="preserve">Kalbyrisvej 55</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,20 +4961,20 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566162</t>
+          <t xml:space="preserve">7045545</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H83">
-        <v>360</v>
+        <v>516</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258446</t>
+          <t xml:space="preserve">311258391</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkehegnet 96</t>
+          <t xml:space="preserve">Korskildevej 2A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5382703</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="H84">
-        <v>557</v>
+        <v>2634</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258381</t>
+          <t xml:space="preserve">311259758</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,35 +5071,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalbyrisvej 55</t>
+          <t xml:space="preserve">Korskildevej 2A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045545</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H85">
-        <v>516</v>
+        <v>266</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258391</t>
+          <t xml:space="preserve">311335367</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,35 +5131,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejlersvej 22</t>
+          <t xml:space="preserve">Korskildevej 2A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025963</t>
+          <t xml:space="preserve">2549311</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H86">
-        <v>676</v>
+        <v>2353</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258430</t>
+          <t xml:space="preserve">311259758</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korskildevej 2A</t>
+          <t xml:space="preserve">Menstrup Bygade 60</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">2528842</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>2634</v>
+        <v>1129</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259758</t>
+          <t xml:space="preserve">311264089</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korskildevej 2A</t>
+          <t xml:space="preserve">Menstrup Bygade 60A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">2528842</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H88">
-        <v>266</v>
+        <v>440</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335367</t>
+          <t xml:space="preserve">311264088</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korskildevej 2A</t>
+          <t xml:space="preserve">Alfehøjvej 85</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549311</t>
+          <t xml:space="preserve">2553620</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>2353</v>
+        <v>980</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259758</t>
+          <t xml:space="preserve">311264735</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menstrup Bygade 60</t>
+          <t xml:space="preserve">Helgesvej 1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528842</t>
+          <t xml:space="preserve">282243, 282244</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>1129</v>
+        <v>1449</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264089</t>
+          <t xml:space="preserve">311264733</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menstrup Bygade 60A</t>
+          <t xml:space="preserve">Holsted Alle 30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528842</t>
+          <t xml:space="preserve">8230221</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H91">
-        <v>440</v>
+        <v>1487</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264088</t>
+          <t xml:space="preserve">311264712</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebakken 27A</t>
+          <t xml:space="preserve">Kasernevej 24</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4736</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526923</t>
+          <t xml:space="preserve">9864070</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,11 +5510,11 @@
         </is>
       </c>
       <c r="H92">
-        <v>281</v>
+        <v>1432</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264737</t>
+          <t xml:space="preserve">311264765</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,17 +5551,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebakken 27B</t>
+          <t xml:space="preserve">Kildegårdsvej 33A</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4736</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526924</t>
+          <t xml:space="preserve">2552585</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5570,11 +5570,11 @@
         </is>
       </c>
       <c r="H93">
-        <v>638</v>
+        <v>372</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264743</t>
+          <t xml:space="preserve">311264772</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdsvej 33A</t>
+          <t xml:space="preserve">Kildegårdsvej 33B</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5626,15 +5626,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H94">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264772</t>
+          <t xml:space="preserve">311264773</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5671,30 +5671,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdsvej 33B</t>
+          <t xml:space="preserve">Kildemarksvej 65</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552585</t>
+          <t xml:space="preserve">5379611</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H95">
-        <v>358</v>
+        <v>987</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264773</t>
+          <t xml:space="preserve">311264761</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alfehøjvej 85</t>
+          <t xml:space="preserve">Kildemarksvej 70</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553620</t>
+          <t xml:space="preserve">5378760</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,11 +5750,11 @@
         </is>
       </c>
       <c r="H96">
-        <v>980</v>
+        <v>760</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264735</t>
+          <t xml:space="preserve">311264767</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 70</t>
+          <t xml:space="preserve">Kirkebakken 27A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4736</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5378760</t>
+          <t xml:space="preserve">2526923</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,11 +5810,11 @@
         </is>
       </c>
       <c r="H97">
-        <v>760</v>
+        <v>281</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264767</t>
+          <t xml:space="preserve">311264737</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5851,17 +5851,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 65</t>
+          <t xml:space="preserve">Kirkebakken 27B</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4736</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5379611</t>
+          <t xml:space="preserve">2526924</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5870,11 +5870,11 @@
         </is>
       </c>
       <c r="H98">
-        <v>987</v>
+        <v>638</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264761</t>
+          <t xml:space="preserve">311264743</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsted Alle 30</t>
+          <t xml:space="preserve">Grønbrovej 1A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4262</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8230221</t>
+          <t xml:space="preserve">2519541</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H101">
-        <v>1487</v>
+        <v>1964</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264712</t>
+          <t xml:space="preserve">311264905</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-08</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 24</t>
+          <t xml:space="preserve">Herlufsholmvej 12</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,25 +6101,25 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9864070</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H102">
-        <v>1432</v>
+        <v>291</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264765</t>
+          <t xml:space="preserve">311265414</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønbrovej 1A</t>
+          <t xml:space="preserve">Herlufsholmvej 12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4262</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2519541</t>
+          <t xml:space="preserve">8152225</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H103">
-        <v>1964</v>
+        <v>372</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264905</t>
+          <t xml:space="preserve">311265418</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-08</t>
+          <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herlufsholmvej 12</t>
+          <t xml:space="preserve">Herlufsholmvej 16</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6286,15 +6286,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H105">
-        <v>291</v>
+        <v>814</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265414</t>
+          <t xml:space="preserve">311265420</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6346,15 +6346,15 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H106">
-        <v>814</v>
+        <v>1442</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265420</t>
+          <t xml:space="preserve">311265409</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herlufsholmvej 12</t>
+          <t xml:space="preserve">Herlufsholmvej 16</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6406,15 +6406,15 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H107">
-        <v>372</v>
+        <v>2136</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265418</t>
+          <t xml:space="preserve">311265411</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6466,15 +6466,15 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H108">
-        <v>1442</v>
+        <v>945</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265409</t>
+          <t xml:space="preserve">311265407</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6526,15 +6526,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H109">
-        <v>2136</v>
+        <v>1453</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265411</t>
+          <t xml:space="preserve">311265413</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herlufsholmvej 16</t>
+          <t xml:space="preserve">Birkebjerg Alle 8</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H110">
-        <v>945</v>
+        <v>648</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265407</t>
+          <t xml:space="preserve">311265983</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herlufsholmvej 16</t>
+          <t xml:space="preserve">Enggårdsvej 3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,25 +6641,25 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8152225</t>
+          <t xml:space="preserve">100019604</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H111">
-        <v>1453</v>
+        <v>3714</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265413</t>
+          <t xml:space="preserve">311266053</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-10</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otterupvej 2</t>
+          <t xml:space="preserve">Enggårdsvej 5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,20 +6701,20 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">100019604</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H112">
-        <v>1008</v>
+        <v>3730</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311266054</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6751,30 +6751,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkebjerg Alle 8</t>
+          <t xml:space="preserve">Gormsvej 24</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">2568762</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>648</v>
+        <v>398</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265989</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,30 +6811,30 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otterupvej 7</t>
+          <t xml:space="preserve">Gormsvej 5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">9802629</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>468</v>
+        <v>791</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265936</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otterupvej 9</t>
+          <t xml:space="preserve">Grimstrupvej 101B</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,20 +6881,20 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">9423768</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>640</v>
+        <v>558</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265934</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6931,30 +6931,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 13</t>
+          <t xml:space="preserve">Holmegaardsvej 56</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">2553381</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>1233</v>
+        <v>605</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265991</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggårdsvej 3</t>
+          <t xml:space="preserve">Kildemarksvej 124</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,20 +7001,20 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019604</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H117">
-        <v>3714</v>
+        <v>2596</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266053</t>
+          <t xml:space="preserve">311266002</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggårdsvej 5</t>
+          <t xml:space="preserve">Kildemarksvej 130</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,20 +7061,20 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019604</t>
+          <t xml:space="preserve">9411350</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H118">
-        <v>3730</v>
+        <v>930</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266054</t>
+          <t xml:space="preserve">311266000</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7171,30 +7171,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 56</t>
+          <t xml:space="preserve">Otterupvej 2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553381</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H120">
-        <v>605</v>
+        <v>1008</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265991</t>
+          <t xml:space="preserve">311265983</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7231,30 +7231,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 24</t>
+          <t xml:space="preserve">Otterupvej 7</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568762</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H121">
-        <v>398</v>
+        <v>468</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265989</t>
+          <t xml:space="preserve">311265983</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 148</t>
+          <t xml:space="preserve">Otterupvej 9</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,20 +7301,20 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381976</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H122">
-        <v>468</v>
+        <v>640</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265947</t>
+          <t xml:space="preserve">311265983</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 21</t>
+          <t xml:space="preserve">Parkvej 148</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,20 +7361,20 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025966</t>
+          <t xml:space="preserve">5381976</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H123">
-        <v>684</v>
+        <v>468</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265931</t>
+          <t xml:space="preserve">311265947</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 130</t>
+          <t xml:space="preserve">Rolighedsvej 21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411350</t>
+          <t xml:space="preserve">9025966</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,11 +7490,11 @@
         </is>
       </c>
       <c r="H125">
-        <v>930</v>
+        <v>684</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266000</t>
+          <t xml:space="preserve">311265931</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 124</t>
+          <t xml:space="preserve">Tommerupvej 13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,20 +7541,20 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H126">
-        <v>2596</v>
+        <v>1233</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266002</t>
+          <t xml:space="preserve">311265983</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimstrupvej 101B</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9423768</t>
+          <t xml:space="preserve">2525530</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,16 +7610,16 @@
         </is>
       </c>
       <c r="H127">
-        <v>558</v>
+        <v>793</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265934</t>
+          <t xml:space="preserve">311266491</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 5</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9802629</t>
+          <t xml:space="preserve">2525530</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H128">
-        <v>791</v>
+        <v>1601</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265936</t>
+          <t xml:space="preserve">311266492</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7726,15 +7726,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H129">
-        <v>793</v>
+        <v>883</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266491</t>
+          <t xml:space="preserve">311266493</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Kindhestegade 16A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525530</t>
+          <t xml:space="preserve">5377367</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130">
-        <v>1601</v>
+        <v>750</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266492</t>
+          <t xml:space="preserve">311267480</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-16</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Maglemølle 10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7841,25 +7841,25 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525530</t>
+          <t xml:space="preserve">8435875</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H131">
-        <v>883</v>
+        <v>330</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266493</t>
+          <t xml:space="preserve">311267435</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-16</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otterupvej 4</t>
+          <t xml:space="preserve">Maglemølle 12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7901,20 +7901,20 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">8435875</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H132">
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267481</t>
+          <t xml:space="preserve">311267441</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otterupvej 5</t>
+          <t xml:space="preserve">Otiumsvej 6A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,20 +7961,20 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">2524028</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H133">
-        <v>468</v>
+        <v>720</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267489</t>
+          <t xml:space="preserve">311267447</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 23</t>
+          <t xml:space="preserve">Otterupvej 4</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8086,15 +8086,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H135">
-        <v>729</v>
+        <v>288</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267430</t>
+          <t xml:space="preserve">311267481</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 25</t>
+          <t xml:space="preserve">Otterupvej 5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="H136">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267418</t>
+          <t xml:space="preserve">311267489</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 27</t>
+          <t xml:space="preserve">Troensevej 10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8206,15 +8206,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="H137">
-        <v>468</v>
+        <v>396</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267421</t>
+          <t xml:space="preserve">311267410</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 10</t>
+          <t xml:space="preserve">Troensevej 23</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8266,15 +8266,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="H138">
-        <v>396</v>
+        <v>729</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267410</t>
+          <t xml:space="preserve">311267430</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otiumsvej 6A</t>
+          <t xml:space="preserve">Troensevej 25</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,20 +8321,20 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2524028</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="H139">
-        <v>720</v>
+        <v>468</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267447</t>
+          <t xml:space="preserve">311267418</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kindhestegade 16A</t>
+          <t xml:space="preserve">Troensevej 27</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8381,20 +8381,20 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377367</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="H140">
-        <v>750</v>
+        <v>468</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267480</t>
+          <t xml:space="preserve">311267421</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglemølle 10</t>
+          <t xml:space="preserve">Lovvænget 3</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8435875</t>
+          <t xml:space="preserve">9018613</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8450,16 +8450,16 @@
         </is>
       </c>
       <c r="H141">
-        <v>330</v>
+        <v>421</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267435</t>
+          <t xml:space="preserve">311269003</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglemølle 12</t>
+          <t xml:space="preserve">Otterupvej 6</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,25 +8501,25 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8435875</t>
+          <t xml:space="preserve">100008684</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H142">
-        <v>341</v>
+        <v>1186</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267441</t>
+          <t xml:space="preserve">311269023</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,30 +8551,30 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otterupvej 6</t>
+          <t xml:space="preserve">Sorøvej 11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008684</t>
+          <t xml:space="preserve">7178336</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H143">
-        <v>1186</v>
+        <v>930</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269023</t>
+          <t xml:space="preserve">311269008</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 11</t>
+          <t xml:space="preserve">Kildemarksvej 116</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7178336</t>
+          <t xml:space="preserve">9874444</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">84</t>
         </is>
       </c>
       <c r="H145">
-        <v>930</v>
+        <v>1199</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269008</t>
+          <t xml:space="preserve">311270528</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovvænget 3</t>
+          <t xml:space="preserve">Ny Præstøvej 200</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,25 +8741,25 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018613</t>
+          <t xml:space="preserve">2566046</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H146">
-        <v>421</v>
+        <v>252</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269003</t>
+          <t xml:space="preserve">311270527</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Præstøvej 200</t>
+          <t xml:space="preserve">Nøddehegnet 110A</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,20 +8801,20 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566046</t>
+          <t xml:space="preserve">9025977</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H147">
-        <v>252</v>
+        <v>470</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270527</t>
+          <t xml:space="preserve">311270529</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøddehegnet 110A</t>
+          <t xml:space="preserve">Hvedevænget 3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025977</t>
+          <t xml:space="preserve">5378977</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,16 +8990,16 @@
         </is>
       </c>
       <c r="H150">
-        <v>470</v>
+        <v>650</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270529</t>
+          <t xml:space="preserve">311271982</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 116</t>
+          <t xml:space="preserve">Marskvej 20A</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,25 +9041,25 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874444</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">84</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>1199</v>
+        <v>2799</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270528</t>
+          <t xml:space="preserve">311271972</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 12</t>
+          <t xml:space="preserve">Marskvej 20B</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,20 +9101,20 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H152">
-        <v>468</v>
+        <v>1251</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271986</t>
+          <t xml:space="preserve">311271975</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Peders Kirkeplads 14A</t>
+          <t xml:space="preserve">Marskvej 22B</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,20 +9161,20 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377582</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H153">
-        <v>1355</v>
+        <v>1280</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271978</t>
+          <t xml:space="preserve">311271973</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Peders Kirkeplads 14C</t>
+          <t xml:space="preserve">Marskvej 22C</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,20 +9221,20 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377582</t>
+          <t xml:space="preserve">5383233</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H154">
-        <v>318</v>
+        <v>1275</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271979</t>
+          <t xml:space="preserve">311271974</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvedevænget 3</t>
+          <t xml:space="preserve">Sct Peders Kirkeplads 14A</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5378977</t>
+          <t xml:space="preserve">5377582</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9290,11 +9290,11 @@
         </is>
       </c>
       <c r="H155">
-        <v>650</v>
+        <v>1355</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271982</t>
+          <t xml:space="preserve">311271978</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marskvej 20A</t>
+          <t xml:space="preserve">Sct Peders Kirkeplads 14C</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">5377582</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H156">
-        <v>2799</v>
+        <v>318</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271972</t>
+          <t xml:space="preserve">311271979</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marskvej 22B</t>
+          <t xml:space="preserve">Tommerupvej 12</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,20 +9401,20 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H157">
-        <v>1280</v>
+        <v>468</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271973</t>
+          <t xml:space="preserve">311271986</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marskvej 22C</t>
+          <t xml:space="preserve">Farimagsvej 16</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9461,25 +9461,25 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">5376904</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H158">
-        <v>1275</v>
+        <v>704</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271974</t>
+          <t xml:space="preserve">311273416</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-18</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,35 +9511,35 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marskvej 20B</t>
+          <t xml:space="preserve">Nattergalevej 1</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5383233</t>
+          <t xml:space="preserve">2518882</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H159">
-        <v>1251</v>
+        <v>1499</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271975</t>
+          <t xml:space="preserve">311273423</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-18</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,35 +9571,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nattergalevej 1</t>
+          <t xml:space="preserve">Helgesvej 7</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518882</t>
+          <t xml:space="preserve">2556040</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H160">
-        <v>1499</v>
+        <v>6683</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311273423</t>
+          <t xml:space="preserve">311275914</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-18</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9631,35 +9631,35 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 16</t>
+          <t xml:space="preserve">Helgesvej 7</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376904</t>
+          <t xml:space="preserve">2556040</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H161">
-        <v>704</v>
+        <v>762</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311273416</t>
+          <t xml:space="preserve">311275916</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-18</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 7</t>
+          <t xml:space="preserve">Helgesvej 9</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,20 +9701,20 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556040</t>
+          <t xml:space="preserve">2556065</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H162">
-        <v>6683</v>
+        <v>357</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275914</t>
+          <t xml:space="preserve">311275917</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 7</t>
+          <t xml:space="preserve">Obovej 11</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556040</t>
+          <t xml:space="preserve">9993538</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>762</v>
+        <v>600</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275914</t>
+          <t xml:space="preserve">311276263</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,35 +9811,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 9</t>
+          <t xml:space="preserve">Obovej 13</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556065</t>
+          <t xml:space="preserve">9993538</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H164">
-        <v>357</v>
+        <v>600</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275917</t>
+          <t xml:space="preserve">311276263</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snerlevej 1</t>
+          <t xml:space="preserve">Obovej 9</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521574</t>
+          <t xml:space="preserve">9993538</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9890,11 +9890,11 @@
         </is>
       </c>
       <c r="H165">
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276140</t>
+          <t xml:space="preserve">311276263</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 2</t>
+          <t xml:space="preserve">Snerlevej 1</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7055783</t>
+          <t xml:space="preserve">2521574</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>921</v>
+        <v>640</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276138</t>
+          <t xml:space="preserve">311276140</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obovej 9</t>
+          <t xml:space="preserve">Storegade 2</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4171</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993538</t>
+          <t xml:space="preserve">7055783</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,11 +10010,11 @@
         </is>
       </c>
       <c r="H167">
-        <v>600</v>
+        <v>921</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276263</t>
+          <t xml:space="preserve">311276138</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,35 +10051,35 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obovej 11</t>
+          <t xml:space="preserve">Holmegaardsvej 15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993538</t>
+          <t xml:space="preserve">8948538</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H168">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276263</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,35 +10111,35 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obovej 13</t>
+          <t xml:space="preserve">Holmegaardsvej 37</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993538</t>
+          <t xml:space="preserve">8948538</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H169">
-        <v>600</v>
+        <v>370</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276263</t>
+          <t xml:space="preserve">311276978</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Villavej 2</t>
+          <t xml:space="preserve">Holmegaardsvej 39</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10186,15 +10186,15 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H170">
-        <v>4765</v>
+        <v>320</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276973</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 37</t>
+          <t xml:space="preserve">Holmegaardsvej 39</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10246,15 +10246,15 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H171">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276978</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 15</t>
+          <t xml:space="preserve">Holmegaardsvej 39</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10306,15 +10306,15 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H172">
-        <v>618</v>
+        <v>1265</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Villavej 2</t>
+          <t xml:space="preserve">Holmegaardsvej 39</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10366,15 +10366,15 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H173">
-        <v>649</v>
+        <v>1380</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276973</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10426,11 +10426,11 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H174">
-        <v>320</v>
+        <v>960</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -10486,11 +10486,11 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H175">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10546,11 +10546,11 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H176">
-        <v>1265</v>
+        <v>413</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 39</t>
+          <t xml:space="preserve">Villavej 2</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10606,15 +10606,15 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H177">
-        <v>1380</v>
+        <v>4765</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276973</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 39</t>
+          <t xml:space="preserve">Villavej 2</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10666,15 +10666,15 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H178">
-        <v>960</v>
+        <v>649</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276973</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,35 +10711,35 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 39</t>
+          <t xml:space="preserve">Birkebjerg Alle 7</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948538</t>
+          <t xml:space="preserve">283841, 283842, 283843</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H179">
-        <v>325</v>
+        <v>5160</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311278159</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 39</t>
+          <t xml:space="preserve">Byagervej 1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948538</t>
+          <t xml:space="preserve">2518929</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H180">
-        <v>413</v>
+        <v>928</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311278224</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,30 +10831,30 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 1</t>
+          <t xml:space="preserve">Grønnegården 2</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518929</t>
+          <t xml:space="preserve">7045792</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H181">
-        <v>928</v>
+        <v>1273</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278224</t>
+          <t xml:space="preserve">311278171</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10891,30 +10891,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvænget 43</t>
+          <t xml:space="preserve">Indre Vordingborgvej 6A</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554718</t>
+          <t xml:space="preserve">7045792</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H182">
-        <v>623</v>
+        <v>916</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278180</t>
+          <t xml:space="preserve">311278170</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indre Vordingborgvej 6A</t>
+          <t xml:space="preserve">Kildemarksvej 114</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10961,20 +10961,20 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045792</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H183">
-        <v>916</v>
+        <v>2186</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278170</t>
+          <t xml:space="preserve">311278199</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegården 2</t>
+          <t xml:space="preserve">Sneppevej 31</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11021,20 +11021,20 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045792</t>
+          <t xml:space="preserve">9130540</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H184">
-        <v>1273</v>
+        <v>4044</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278171</t>
+          <t xml:space="preserve">311278153</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,30 +11071,30 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sneppevej 31</t>
+          <t xml:space="preserve">Søvænget 43</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4171</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130540</t>
+          <t xml:space="preserve">2554718</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H185">
-        <v>4044</v>
+        <v>623</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278153</t>
+          <t xml:space="preserve">311278180</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 114</t>
+          <t xml:space="preserve">Karrebækvej 70</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,25 +11141,25 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">7515058</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H186">
-        <v>2186</v>
+        <v>1875</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278199</t>
+          <t xml:space="preserve">311278940</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-12</t>
+          <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11206,15 +11206,15 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H187">
-        <v>1875</v>
+        <v>542</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278940</t>
+          <t xml:space="preserve">311278942</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11266,15 +11266,15 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H188">
-        <v>542</v>
+        <v>493</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278942</t>
+          <t xml:space="preserve">311278941</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11326,15 +11326,15 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H189">
-        <v>493</v>
+        <v>1186</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278941</t>
+          <t xml:space="preserve">311278942</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11386,15 +11386,15 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H190">
-        <v>1186</v>
+        <v>2576</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278942</t>
+          <t xml:space="preserve">311278944</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karrebækvej 80</t>
+          <t xml:space="preserve">Karrebækvej 70</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11446,15 +11446,15 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H191">
-        <v>618</v>
+        <v>1216</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278943</t>
+          <t xml:space="preserve">311278945</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11506,15 +11506,15 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H192">
-        <v>2576</v>
+        <v>493</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278944</t>
+          <t xml:space="preserve">311278941</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11566,15 +11566,15 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H193">
-        <v>1216</v>
+        <v>493</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278945</t>
+          <t xml:space="preserve">311278941</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H194">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karrebækvej 70</t>
+          <t xml:space="preserve">Karrebækvej 80</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11686,15 +11686,15 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H195">
-        <v>493</v>
+        <v>618</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278941</t>
+          <t xml:space="preserve">311278943</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11731,35 +11731,35 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karrebækvej 70</t>
+          <t xml:space="preserve">Sandvedvej 20A</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7515058</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H196">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278941</t>
+          <t xml:space="preserve">311279855</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-17</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvedvej 20A</t>
+          <t xml:space="preserve">Sandvedvej 24</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12046,15 +12046,15 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H201">
-        <v>427</v>
+        <v>330</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279855</t>
+          <t xml:space="preserve">311279850</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12106,15 +12106,15 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H202">
-        <v>330</v>
+        <v>877</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279850</t>
+          <t xml:space="preserve">311279856</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12151,35 +12151,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvedvej 24</t>
+          <t xml:space="preserve">Kærvej 5A</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">2556073</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H203">
-        <v>877</v>
+        <v>530</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279856</t>
+          <t xml:space="preserve">311282264</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12211,17 +12211,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smidstrupvej 3A</t>
+          <t xml:space="preserve">Nyvej 11</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4171</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549637</t>
+          <t xml:space="preserve">2554666</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -12230,11 +12230,11 @@
         </is>
       </c>
       <c r="H204">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282253</t>
+          <t xml:space="preserve">311282280</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12271,17 +12271,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 1</t>
+          <t xml:space="preserve">Skovburren 1</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554460</t>
+          <t xml:space="preserve">8285703</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -12290,11 +12290,11 @@
         </is>
       </c>
       <c r="H205">
-        <v>479</v>
+        <v>1008</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282292</t>
+          <t xml:space="preserve">311282290</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12331,17 +12331,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 11</t>
+          <t xml:space="preserve">Smidstrupvej 3A</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2554666</t>
+          <t xml:space="preserve">2549637</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12350,11 +12350,11 @@
         </is>
       </c>
       <c r="H206">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282280</t>
+          <t xml:space="preserve">311282253</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12451,17 +12451,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 5A</t>
+          <t xml:space="preserve">Torvet 1</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4171</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556073</t>
+          <t xml:space="preserve">2554460</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12470,11 +12470,11 @@
         </is>
       </c>
       <c r="H208">
-        <v>530</v>
+        <v>479</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282264</t>
+          <t xml:space="preserve">311282292</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12511,17 +12511,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovburren 1</t>
+          <t xml:space="preserve">Kirkebakken 41</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4736</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285703</t>
+          <t xml:space="preserve">2526918</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -12530,16 +12530,16 @@
         </is>
       </c>
       <c r="H209">
-        <v>1008</v>
+        <v>3254</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282290</t>
+          <t xml:space="preserve">311283203</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-06</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12586,15 +12586,15 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H210">
-        <v>3254</v>
+        <v>448</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283203</t>
+          <t xml:space="preserve">311283201</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12646,15 +12646,15 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H211">
-        <v>448</v>
+        <v>1825</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283201</t>
+          <t xml:space="preserve">311283199</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12691,17 +12691,17 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebakken 41</t>
+          <t xml:space="preserve">Åsøvej 7A</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4736</t>
+          <t xml:space="preserve">4171</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2526918</t>
+          <t xml:space="preserve">8992191</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -12710,11 +12710,11 @@
         </is>
       </c>
       <c r="H212">
-        <v>1825</v>
+        <v>1632</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283199</t>
+          <t xml:space="preserve">311283241</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åsøvej 7D</t>
+          <t xml:space="preserve">Åsøvej 7C</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12766,15 +12766,15 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H213">
-        <v>477</v>
+        <v>419</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283239</t>
+          <t xml:space="preserve">311283240</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åsøvej 7A</t>
+          <t xml:space="preserve">Åsøvej 7D</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12826,15 +12826,15 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H214">
-        <v>1632</v>
+        <v>477</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283241</t>
+          <t xml:space="preserve">311283239</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12871,35 +12871,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åsøvej 7C</t>
+          <t xml:space="preserve">Birkevænget 199</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">8992191</t>
+          <t xml:space="preserve">8199232</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H215">
-        <v>419</v>
+        <v>501</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283240</t>
+          <t xml:space="preserve">311283492</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12931,30 +12931,30 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svingkærvej 50</t>
+          <t xml:space="preserve">Birkevænget 55</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">100058876</t>
+          <t xml:space="preserve">8199232</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H216">
-        <v>522</v>
+        <v>1783</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283475</t>
+          <t xml:space="preserve">311283492</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandværksvej 27A</t>
+          <t xml:space="preserve">Birkevænget 57</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13001,20 +13001,20 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2555331</t>
+          <t xml:space="preserve">8199232</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H217">
-        <v>269</v>
+        <v>632</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283471</t>
+          <t xml:space="preserve">311283492</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådmandshaven 20</t>
+          <t xml:space="preserve">Kildemarksvej 128</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13061,20 +13061,20 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">8154549</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H218">
-        <v>14334</v>
+        <v>3558</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283588</t>
+          <t xml:space="preserve">311283479</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -13111,30 +13111,30 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevænget 199</t>
+          <t xml:space="preserve">Rådmandshaven 20</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8199232</t>
+          <t xml:space="preserve">8154549</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H219">
-        <v>501</v>
+        <v>14334</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283492</t>
+          <t xml:space="preserve">311283588</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -13171,30 +13171,30 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevænget 55</t>
+          <t xml:space="preserve">Sneppevej 13A</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8199232</t>
+          <t xml:space="preserve">9948685</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H220">
-        <v>1783</v>
+        <v>276</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283492</t>
+          <t xml:space="preserve">311283510</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13231,30 +13231,30 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevænget 57</t>
+          <t xml:space="preserve">Sneppevej 17A</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8199232</t>
+          <t xml:space="preserve">9948685</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H221">
-        <v>632</v>
+        <v>276</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283492</t>
+          <t xml:space="preserve">311283510</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tove Ditlevsens Vej 8</t>
+          <t xml:space="preserve">Sneppevej 21A</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13301,20 +13301,20 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130926</t>
+          <t xml:space="preserve">9948685</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H222">
-        <v>1900</v>
+        <v>276</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283476</t>
+          <t xml:space="preserve">311283510</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 128</t>
+          <t xml:space="preserve">Sneppevej 3A</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">9948685</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -13370,11 +13370,11 @@
         </is>
       </c>
       <c r="H223">
-        <v>3558</v>
+        <v>616</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283479</t>
+          <t xml:space="preserve">311283509</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13471,30 +13471,30 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sneppevej 3A</t>
+          <t xml:space="preserve">Svingkærvej 50</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4733</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">9948685</t>
+          <t xml:space="preserve">100058876</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H225">
-        <v>616</v>
+        <v>522</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283508</t>
+          <t xml:space="preserve">311283475</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sneppevej 13A</t>
+          <t xml:space="preserve">Tove Ditlevsens Vej 8</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13541,20 +13541,20 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">9948685</t>
+          <t xml:space="preserve">9130926</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H226">
-        <v>276</v>
+        <v>1900</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311283476</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13591,30 +13591,30 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sneppevej 17A</t>
+          <t xml:space="preserve">Vandværksvej 27A</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">9948685</t>
+          <t xml:space="preserve">2555331</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H227">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311283471</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sneppevej 21A</t>
+          <t xml:space="preserve">Dybsøvej 66</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13661,25 +13661,25 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9948685</t>
+          <t xml:space="preserve">8523169</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H228">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311284308</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-11-17</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -13831,35 +13831,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dybsøvej 66</t>
+          <t xml:space="preserve">Gartnervænget 10</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4160</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8523169</t>
+          <t xml:space="preserve">2555839</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H231">
-        <v>277</v>
+        <v>427</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284308</t>
+          <t xml:space="preserve">311284650</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-17</t>
+          <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -13891,30 +13891,30 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervænget 10</t>
+          <t xml:space="preserve">Jasminvej 1</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2555839</t>
+          <t xml:space="preserve">9124197</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H232">
-        <v>427</v>
+        <v>1793</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284650</t>
+          <t xml:space="preserve">311284631</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Præstøvej 304</t>
+          <t xml:space="preserve">Jasminvej 3</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13961,20 +13961,20 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025902</t>
+          <t xml:space="preserve">9124197</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H233">
-        <v>273</v>
+        <v>1793</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284647</t>
+          <t xml:space="preserve">311284632</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasminvej 1</t>
+          <t xml:space="preserve">Jasminvej 5A</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -14026,15 +14026,15 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H234">
-        <v>1793</v>
+        <v>588</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284631</t>
+          <t xml:space="preserve">311284632</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasminvej 3</t>
+          <t xml:space="preserve">Jasminvej 9A</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14086,11 +14086,11 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H235">
-        <v>1793</v>
+        <v>589</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasminvej 5A</t>
+          <t xml:space="preserve">Ny Præstøvej 304</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14141,20 +14141,20 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124197</t>
+          <t xml:space="preserve">9025902</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H236">
-        <v>588</v>
+        <v>273</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284632</t>
+          <t xml:space="preserve">311284647</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasminvej 9A</t>
+          <t xml:space="preserve">Manøvej 25</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14201,25 +14201,25 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124197</t>
+          <t xml:space="preserve">5380770</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H237">
-        <v>589</v>
+        <v>4975</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284632</t>
+          <t xml:space="preserve">311285143</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-20</t>
+          <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manøvej 25</t>
+          <t xml:space="preserve">Manøvej 25A</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14266,11 +14266,11 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H238">
-        <v>4975</v>
+        <v>948</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manøvej 25A</t>
+          <t xml:space="preserve">Nygårdsvej 110</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14321,20 +14321,20 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380770</t>
+          <t xml:space="preserve">5382706</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H239">
-        <v>948</v>
+        <v>4228</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285143</t>
+          <t xml:space="preserve">311285115</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 110</t>
+          <t xml:space="preserve">Stationsvej 49A</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5382706</t>
+          <t xml:space="preserve">2565303</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -14450,16 +14450,16 @@
         </is>
       </c>
       <c r="H241">
-        <v>4228</v>
+        <v>2045</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285115</t>
+          <t xml:space="preserve">311285802</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-22</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14491,30 +14491,30 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensevej 13</t>
+          <t xml:space="preserve">Stationsvej 49B</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005589</t>
+          <t xml:space="preserve">2565303</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H242">
-        <v>464</v>
+        <v>371</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285853</t>
+          <t xml:space="preserve">311285803</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 49A</t>
+          <t xml:space="preserve">Stationsvej 49E</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14566,15 +14566,15 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H243">
-        <v>2045</v>
+        <v>371</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285802</t>
+          <t xml:space="preserve">311285801</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14611,30 +14611,30 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 49B</t>
+          <t xml:space="preserve">Troensevej 13</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2565303</t>
+          <t xml:space="preserve">100005589</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="H244">
-        <v>371</v>
+        <v>464</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285803</t>
+          <t xml:space="preserve">311285853</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 49E</t>
+          <t xml:space="preserve">Toksværd Bygade 56A</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14681,25 +14681,25 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2565303</t>
+          <t xml:space="preserve">8192189</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H245">
-        <v>371</v>
+        <v>445</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285801</t>
+          <t xml:space="preserve">311286034</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -14731,17 +14731,17 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toksværd Bygade 56A</t>
+          <t xml:space="preserve">Ved Åsen 1</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">8192189</t>
+          <t xml:space="preserve">5377816</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -14750,16 +14750,16 @@
         </is>
       </c>
       <c r="H246">
-        <v>445</v>
+        <v>1926</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286034</t>
+          <t xml:space="preserve">311286334</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Åsen 1</t>
+          <t xml:space="preserve">Ved Åsen 12</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377816</t>
+          <t xml:space="preserve">5377830</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -14810,11 +14810,11 @@
         </is>
       </c>
       <c r="H247">
-        <v>1926</v>
+        <v>554</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286334</t>
+          <t xml:space="preserve">311286332</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14866,15 +14866,15 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H248">
-        <v>554</v>
+        <v>284</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286332</t>
+          <t xml:space="preserve">311286331</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H249">
@@ -14971,35 +14971,35 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Åsen 12</t>
+          <t xml:space="preserve">Falkevænget 9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5377830</t>
+          <t xml:space="preserve">2518884</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H250">
-        <v>284</v>
+        <v>820</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286331</t>
+          <t xml:space="preserve">311286568</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkevænget 9</t>
+          <t xml:space="preserve">Haldagermaglevej 6</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518884</t>
+          <t xml:space="preserve">2528563</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -15050,11 +15050,11 @@
         </is>
       </c>
       <c r="H251">
-        <v>820</v>
+        <v>1340</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286568</t>
+          <t xml:space="preserve">311286570</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15091,17 +15091,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haldagermaglevej 6</t>
+          <t xml:space="preserve">Holsted Alle 30</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528563</t>
+          <t xml:space="preserve">8230221</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -15110,16 +15110,16 @@
         </is>
       </c>
       <c r="H252">
-        <v>1340</v>
+        <v>9563</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286570</t>
+          <t xml:space="preserve">311286776</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-01</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -15151,30 +15151,30 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tokesvej 1</t>
+          <t xml:space="preserve">Holsted Alle 32</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003883</t>
+          <t xml:space="preserve">8230221</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H253">
-        <v>2462</v>
+        <v>940</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286774</t>
+          <t xml:space="preserve">311286775</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -15226,11 +15226,11 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H254">
-        <v>1909</v>
+        <v>2462</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -15271,30 +15271,30 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsted Alle 30</t>
+          <t xml:space="preserve">Tokesvej 1</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">8230221</t>
+          <t xml:space="preserve">7003883</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H255">
-        <v>9563</v>
+        <v>1909</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286776</t>
+          <t xml:space="preserve">311286774</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsted Alle 32</t>
+          <t xml:space="preserve">Obovej 5</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -15341,25 +15341,25 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8230221</t>
+          <t xml:space="preserve">9130468</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H256">
-        <v>940</v>
+        <v>4476</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286775</t>
+          <t xml:space="preserve">311287008</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-01</t>
+          <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 17A</t>
+          <t xml:space="preserve">Obovej 6</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -15401,20 +15401,20 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196771</t>
+          <t xml:space="preserve">9130468</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H257">
-        <v>406</v>
+        <v>1320</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286986</t>
+          <t xml:space="preserve">311287009</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 18A</t>
+          <t xml:space="preserve">Tommerupvej 17A</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -15466,15 +15466,15 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H258">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286963</t>
+          <t xml:space="preserve">311286986</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 19A</t>
+          <t xml:space="preserve">Tommerupvej 18A</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H259">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286994</t>
+          <t xml:space="preserve">311286963</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 21A</t>
+          <t xml:space="preserve">Tommerupvej 19A</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -15586,15 +15586,15 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H260">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286996</t>
+          <t xml:space="preserve">311286987</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 23A</t>
+          <t xml:space="preserve">Tommerupvej 20A</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15646,15 +15646,15 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H261">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286989</t>
+          <t xml:space="preserve">311286962</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 25A</t>
+          <t xml:space="preserve">Tommerupvej 21A</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H262">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286990</t>
+          <t xml:space="preserve">311286988</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 24A</t>
+          <t xml:space="preserve">Tommerupvej 22A</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H263">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286960</t>
+          <t xml:space="preserve">311286961</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 22A</t>
+          <t xml:space="preserve">Tommerupvej 23A</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15826,15 +15826,15 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H264">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286961</t>
+          <t xml:space="preserve">311286989</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 20A</t>
+          <t xml:space="preserve">Tommerupvej 24A</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H265">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286962</t>
+          <t xml:space="preserve">311286960</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15931,30 +15931,30 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trollesgave 4</t>
+          <t xml:space="preserve">Tommerupvej 25A</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">4684</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">8115385</t>
+          <t xml:space="preserve">7196771</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H266">
-        <v>983</v>
+        <v>406</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286976</t>
+          <t xml:space="preserve">311286990</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trollesgave 5</t>
+          <t xml:space="preserve">Trollesgave 4</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -16006,15 +16006,15 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H267">
-        <v>460</v>
+        <v>983</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286977</t>
+          <t xml:space="preserve">311286976</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trollesgave 6</t>
+          <t xml:space="preserve">Trollesgave 5</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -16066,15 +16066,15 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H268">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286978</t>
+          <t xml:space="preserve">311286977</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16111,30 +16111,30 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obovej 5</t>
+          <t xml:space="preserve">Trollesgave 6</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4684</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130468</t>
+          <t xml:space="preserve">8115385</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H269">
-        <v>4476</v>
+        <v>490</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287008</t>
+          <t xml:space="preserve">311286978</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obovej 6</t>
+          <t xml:space="preserve">Obovej 7</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -16181,25 +16181,25 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130468</t>
+          <t xml:space="preserve">9993537</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H270">
-        <v>1320</v>
+        <v>608</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287009</t>
+          <t xml:space="preserve">311287819</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-04</t>
+          <t xml:space="preserve">2027-12-08</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obovej 7</t>
+          <t xml:space="preserve">Lovvej 3</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993537</t>
+          <t xml:space="preserve">9018641</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -16310,16 +16310,16 @@
         </is>
       </c>
       <c r="H272">
-        <v>608</v>
+        <v>1156</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287819</t>
+          <t xml:space="preserve">311288520</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-08</t>
+          <t xml:space="preserve">2027-12-13</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovvej 3</t>
+          <t xml:space="preserve">Lovvej 3E</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -16366,11 +16366,11 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H273">
-        <v>1156</v>
+        <v>368</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -16411,35 +16411,35 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovvej 3E</t>
+          <t xml:space="preserve">Kildegårdsvej 3</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4736</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018641</t>
+          <t xml:space="preserve">8746444</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H274">
-        <v>368</v>
+        <v>1046</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288520</t>
+          <t xml:space="preserve">311288798</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-13</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 7</t>
+          <t xml:space="preserve">Kildemarksvej 118</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -16481,20 +16481,20 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008683</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H275">
-        <v>1263</v>
+        <v>932</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288809</t>
+          <t xml:space="preserve">311288792</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -16531,30 +16531,30 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdsvej 3</t>
+          <t xml:space="preserve">Kildemarksvej 120</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">4736</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">8746444</t>
+          <t xml:space="preserve">9411351</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H276">
-        <v>1046</v>
+        <v>946</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288798</t>
+          <t xml:space="preserve">311288794</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 120</t>
+          <t xml:space="preserve">Tommerupvej 7</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -16661,20 +16661,20 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">100008683</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H278">
-        <v>946</v>
+        <v>1263</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288794</t>
+          <t xml:space="preserve">311288809</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -16711,35 +16711,35 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildemarksvej 118</t>
+          <t xml:space="preserve">Kildegårdsvej 5</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700</t>
+          <t xml:space="preserve">4736</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">9411351</t>
+          <t xml:space="preserve">8746444</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H279">
-        <v>932</v>
+        <v>1058</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288792</t>
+          <t xml:space="preserve">311288987</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -16771,30 +16771,30 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvedvej 24</t>
+          <t xml:space="preserve">Kildegårdsvej 7</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4250</t>
+          <t xml:space="preserve">4736</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518970</t>
+          <t xml:space="preserve">8746444</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H280">
-        <v>589</v>
+        <v>1046</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288912</t>
+          <t xml:space="preserve">311288990</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -16831,30 +16831,30 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdsvej 5</t>
+          <t xml:space="preserve">Sandvedvej 24</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">4736</t>
+          <t xml:space="preserve">4250</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">8746444</t>
+          <t xml:space="preserve">2518970</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H281">
-        <v>1058</v>
+        <v>589</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288987</t>
+          <t xml:space="preserve">311288912</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -16891,35 +16891,35 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdsvej 7</t>
+          <t xml:space="preserve">Blegdammen 3</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">4736</t>
+          <t xml:space="preserve">4700</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">8746444</t>
+          <t xml:space="preserve">5381277</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H282">
-        <v>1046</v>
+        <v>285</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288990</t>
+          <t xml:space="preserve">311289156</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 44A</t>
+          <t xml:space="preserve">Blegdammen 5</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16961,20 +16961,20 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">100004810</t>
+          <t xml:space="preserve">5381277</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H283">
-        <v>480</v>
+        <v>285</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289149</t>
+          <t xml:space="preserve">311289156</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 46A</t>
+          <t xml:space="preserve">Farimagsvej 44A</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17026,15 +17026,15 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H284">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289150</t>
+          <t xml:space="preserve">311289149</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 48A</t>
+          <t xml:space="preserve">Farimagsvej 46A</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H285">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289151</t>
+          <t xml:space="preserve">311289150</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 50A</t>
+          <t xml:space="preserve">Farimagsvej 48A</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -17146,15 +17146,15 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H286">
-        <v>252</v>
+        <v>504</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289152</t>
+          <t xml:space="preserve">311289151</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrænten 1</t>
+          <t xml:space="preserve">Farimagsvej 50A</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -17201,20 +17201,20 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564018</t>
+          <t xml:space="preserve">100004810</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H287">
-        <v>396</v>
+        <v>252</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289158</t>
+          <t xml:space="preserve">311289152</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebæksholm 2</t>
+          <t xml:space="preserve">Farimagsvej 67</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -17261,20 +17261,20 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566043</t>
+          <t xml:space="preserve">7045143</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H288">
-        <v>593</v>
+        <v>480</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289142</t>
+          <t xml:space="preserve">311289148</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 7A</t>
+          <t xml:space="preserve">Nygårdsvej 100</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5380077</t>
+          <t xml:space="preserve">7751582</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -17390,11 +17390,11 @@
         </is>
       </c>
       <c r="H290">
-        <v>334</v>
+        <v>2147</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289160</t>
+          <t xml:space="preserve">311289139</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blegdammen 3</t>
+          <t xml:space="preserve">Nygårdsvej 100B</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381277</t>
+          <t xml:space="preserve">7751582</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -17450,11 +17450,11 @@
         </is>
       </c>
       <c r="H291">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289156</t>
+          <t xml:space="preserve">311289140</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blegdammen 5</t>
+          <t xml:space="preserve">Omøvej 3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H292">
@@ -17551,7 +17551,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omøvej 3</t>
+          <t xml:space="preserve">Rønnebæksholm 2</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">5381277</t>
+          <t xml:space="preserve">2566043</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -17570,11 +17570,11 @@
         </is>
       </c>
       <c r="H293">
-        <v>285</v>
+        <v>593</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289156</t>
+          <t xml:space="preserve">311289142</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farimagsvej 67</t>
+          <t xml:space="preserve">Skrænten 1</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -17621,7 +17621,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">7045143</t>
+          <t xml:space="preserve">2564018</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -17630,11 +17630,11 @@
         </is>
       </c>
       <c r="H294">
-        <v>480</v>
+        <v>396</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289148</t>
+          <t xml:space="preserve">311289158</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 16A</t>
+          <t xml:space="preserve">Tommerupvej 14</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -17686,7 +17686,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H295">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommerupvej 14</t>
+          <t xml:space="preserve">Tommerupvej 16A</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H296">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 100</t>
+          <t xml:space="preserve">Tommerupvej 2B</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">7751582</t>
+          <t xml:space="preserve">283503, 283840</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -17810,11 +17810,11 @@
         </is>
       </c>
       <c r="H297">
-        <v>2147</v>
+        <v>3100</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289139</t>
+          <t xml:space="preserve">311289255</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -17851,7 +17851,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 100B</t>
+          <t xml:space="preserve">Ågade 7A</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -17861,20 +17861,20 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">7751582</t>
+          <t xml:space="preserve">5380077</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H298">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289140</t>
+          <t xml:space="preserve">311289160</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teatergade 8</t>
+          <t xml:space="preserve">Teatergade 6</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -18166,15 +18166,15 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H303">
-        <v>4108</v>
+        <v>854</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290712</t>
+          <t xml:space="preserve">311290713</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teatergade 6</t>
+          <t xml:space="preserve">Teatergade 8</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -18226,15 +18226,15 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H304">
-        <v>854</v>
+        <v>4108</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290713</t>
+          <t xml:space="preserve">311290712</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovvej 3B</t>
+          <t xml:space="preserve">Grimstrupvej 131D</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -18941,20 +18941,20 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018641</t>
+          <t xml:space="preserve">9025993</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H316">
-        <v>777</v>
+        <v>375</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291684</t>
+          <t xml:space="preserve">311291806</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
@@ -18991,7 +18991,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovvej 3C</t>
+          <t xml:space="preserve">Kasernevej 17</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -19001,20 +19001,20 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">9018641</t>
+          <t xml:space="preserve">9874447</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H317">
-        <v>820</v>
+        <v>1738</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291684</t>
+          <t xml:space="preserve">311291678</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovvej 3D</t>
+          <t xml:space="preserve">Lovvej 3B</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -19066,11 +19066,11 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H318">
-        <v>645</v>
+        <v>777</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimstrupvej 131D</t>
+          <t xml:space="preserve">Lovvej 3C</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -19121,20 +19121,20 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">9025993</t>
+          <t xml:space="preserve">9018641</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H319">
-        <v>375</v>
+        <v>820</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291806</t>
+          <t xml:space="preserve">311291684</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 17</t>
+          <t xml:space="preserve">Lovvej 3D</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -19181,20 +19181,20 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874447</t>
+          <t xml:space="preserve">9018641</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H320">
-        <v>1738</v>
+        <v>645</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291678</t>
+          <t xml:space="preserve">311291684</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296826</t>
+          <t xml:space="preserve">311296823</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296826</t>
+          <t xml:space="preserve">311296824</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">

--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -12894,7 +12894,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283492</t>
+          <t xml:space="preserve">311283491</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283492</t>
+          <t xml:space="preserve">311283491</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283492</t>
+          <t xml:space="preserve">311283491</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">

--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -9654,7 +9654,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275916</t>
+          <t xml:space="preserve">311275914</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276978</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276969</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276973</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276973</t>
+          <t xml:space="preserve">311276977</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286961</t>
+          <t xml:space="preserve">311286965</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286989</t>
+          <t xml:space="preserve">311286999</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286960</t>
+          <t xml:space="preserve">311286964</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296823</t>
+          <t xml:space="preserve">311296826</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296824</t>
+          <t xml:space="preserve">311296826</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">

--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L329"/>
+  <dimension ref="A1:M329"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Nykøbing F</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-30</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-24</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-06</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-15</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3114,20 +3369,25 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252543</t>
+          <t xml:space="preserve">311252552</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3174,20 +3434,25 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252545</t>
+          <t xml:space="preserve">311252552</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3294,20 +3564,25 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252549</t>
+          <t xml:space="preserve">311252552</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3354,20 +3629,25 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252554</t>
+          <t xml:space="preserve">311252552</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-08</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-08</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-10</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6594,20 +7139,25 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7194,20 +7789,25 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7254,20 +7854,25 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7314,20 +7919,25 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7554,20 +8179,25 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265983</t>
+          <t xml:space="preserve">311265981</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-16</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-04</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-18</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-18</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-17</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-06</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-17</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-17</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-17</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-20</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-01</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-01</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-01</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-01</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15474,20 +16759,25 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286986</t>
+          <t xml:space="preserve">311286993</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15594,20 +16889,25 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286987</t>
+          <t xml:space="preserve">311286994</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15654,20 +16954,25 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286962</t>
+          <t xml:space="preserve">311286966</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15894,20 +17214,25 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286964</t>
+          <t xml:space="preserve">311286960</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-08</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16259,15 +17609,20 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-08</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16319,15 +17674,20 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-13</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16379,15 +17739,20 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-13</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16439,15 +17804,20 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16499,15 +17869,20 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16559,15 +17934,20 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16619,15 +17999,20 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16679,15 +18064,20 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16739,15 +18129,20 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16799,15 +18194,20 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16859,15 +18259,20 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16919,15 +18324,20 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16979,15 +18389,20 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17039,15 +18454,20 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17099,15 +18519,20 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17159,15 +18584,20 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17219,15 +18649,20 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17279,15 +18714,20 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17339,15 +18779,20 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17399,15 +18844,20 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17459,15 +18909,20 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17519,15 +18974,20 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17579,15 +19039,20 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17639,15 +19104,20 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17699,15 +19169,20 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17759,15 +19234,20 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17819,15 +19299,20 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17879,15 +19364,20 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17939,15 +19429,20 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17999,15 +19494,20 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18059,15 +19559,20 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18119,15 +19624,20 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18179,15 +19689,20 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18239,15 +19754,20 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18299,15 +19819,20 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18359,15 +19884,20 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18419,15 +19949,20 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18479,15 +20014,20 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18539,15 +20079,20 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18599,15 +20144,20 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18659,15 +20209,20 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18719,15 +20274,20 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18779,15 +20339,20 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18839,15 +20404,20 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18899,15 +20469,20 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-03</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18959,15 +20534,20 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19019,15 +20599,20 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19079,15 +20664,20 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19139,15 +20729,20 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19199,15 +20794,20 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19254,20 +20854,25 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296826</t>
+          <t xml:space="preserve">311296823</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19314,20 +20919,25 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296826</t>
+          <t xml:space="preserve">311296824</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19379,15 +20989,20 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
+          <t xml:space="preserve">Murbyg ApS</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-20</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19439,15 +21054,20 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19499,15 +21119,20 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19559,15 +21184,20 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19619,15 +21249,20 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-22</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19679,15 +21314,20 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
+          <t xml:space="preserve">TP-Design ApS</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19739,21 +21379,26 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L329" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L329"/>
+  <autoFilter ref="A1:M329"/>
 </worksheet>
 </file>
--- a/public/exports/29189625.xlsx
+++ b/public/exports/29189625.xlsx
@@ -3369,7 +3369,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252552</t>
+          <t xml:space="preserve">311252543</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252552</t>
+          <t xml:space="preserve">311252545</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252552</t>
+          <t xml:space="preserve">311252549</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269008</t>
+          <t xml:space="preserve">311269007</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11429,12 +11429,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276969</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276973</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276977</t>
+          <t xml:space="preserve">311276973</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -14289,12 +14289,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283510</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -14484,12 +14484,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283509</t>
+          <t xml:space="preserve">311283508</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286774</t>
+          <t xml:space="preserve">311286773</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286774</t>
+          <t xml:space="preserve">311286773</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286993</t>
+          <t xml:space="preserve">311286986</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286994</t>
+          <t xml:space="preserve">311286987</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286966</t>
+          <t xml:space="preserve">311286962</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286965</t>
+          <t xml:space="preserve">311286961</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286999</t>
+          <t xml:space="preserve">311286989</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
